--- a/SIMULATION/EXPERIMENT MODEL/START/rekomendasi_paket_flexible.xlsx
+++ b/SIMULATION/EXPERIMENT MODEL/START/rekomendasi_paket_flexible.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:Z31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,80 +457,105 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Wilayah Hotel</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Nama Wisata</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Harga Wisata (Satuan)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Total Biaya Wisata</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Wilayah Wisata</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Nama Kuliner Pagi</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Harga Kuliner Pagi</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Nama Kuliner Siang</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Harga Kuliner Siang</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Nama Kuliner Malam</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Harga Kuliner Malam</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Total Biaya Kuliner</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Wilayah Kuliner</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Rute Transport (Jarak km)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Armada Transport</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Biaya Transport</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Estimasi Total Biaya</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Total Budget Input</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Sisa Anggaran</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Kelebihan Anggaran</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -547,71 +572,94 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hotel Asida</t>
+          <t>The New Handayani Villa's</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="E2" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Air Terjun Coban Jahe</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Air Terjun Coban Talun</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>12000</v>
       </c>
-      <c r="H2" t="n">
-        <v>24000</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Waroeng Watu Gong</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>15250</v>
+      <c r="I2" t="n">
+        <v>24500</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Warung Biru Lesti</t>
+          <t>Warung Berkah</t>
         </is>
       </c>
       <c r="L2" t="n">
         <v>15000</v>
       </c>
-      <c r="M2" t="n">
-        <v>75750</v>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Warung Jawa Sohibul Barokah</t>
+        </is>
       </c>
       <c r="N2" t="n">
-        <v>129.4</v>
+        <v>15000</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
+          <t>Warung Sumber Rejeki 2</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>75000</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P2" t="n">
-        <v>291140</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>525661</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>63158</v>
+      </c>
+      <c r="V2" t="n">
+        <v>300484</v>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -639,60 +687,83 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Air Terjun Coban Jahe</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>12000</v>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SAWAH GENTING</t>
+        </is>
       </c>
       <c r="H3" t="n">
-        <v>24000</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Warung Bu Erni</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>15350</v>
+        <v>12500</v>
+      </c>
+      <c r="I3" t="n">
+        <v>25500</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>Warung Sumber Rejeki 2</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Warung Berkah</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>15000</v>
-      </c>
-      <c r="M3" t="n">
-        <v>75750</v>
-      </c>
-      <c r="N3" t="n">
-        <v>129.4</v>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>75250</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P3" t="n">
-        <v>291140</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>525661</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>63232</v>
+      </c>
+      <c r="V3" t="n">
+        <v>298753</v>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -720,60 +791,83 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Air Terjun Coban Jahe</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Air Terjun Coban Talun</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>12000</v>
       </c>
-      <c r="H4" t="n">
-        <v>24000</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Waroeng Gaul Oeloeng</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>15400</v>
+      <c r="I4" t="n">
+        <v>24500</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>Warung Sumber Rejeki 2</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Warung Berkah</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>15000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>75750</v>
-      </c>
-      <c r="N4" t="n">
-        <v>129.4</v>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P4" t="n">
-        <v>291140</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>525661</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>64233</v>
+      </c>
+      <c r="V4" t="n">
+        <v>298504</v>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -790,71 +884,94 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hotel Asida</t>
+          <t>The New Handayani Villa's</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="E5" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Air Terjun Coban Jahe</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>12000</v>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SAWAH GENTING</t>
+        </is>
       </c>
       <c r="H5" t="n">
-        <v>24000</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Warung Rujak Mbak Camik</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>15000</v>
+        <v>12500</v>
+      </c>
+      <c r="I5" t="n">
+        <v>24500</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Warung Biru Lesti</t>
+          <t>Warung Berkah</t>
         </is>
       </c>
       <c r="L5" t="n">
         <v>15000</v>
       </c>
-      <c r="M5" t="n">
-        <v>75750</v>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Warung Jawa Sohibul Barokah</t>
+        </is>
       </c>
       <c r="N5" t="n">
-        <v>129.4</v>
+        <v>15000</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>Warung Sumber Rejeki 2</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>75000</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P5" t="n">
-        <v>291140</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>525661</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>64248</v>
+      </c>
+      <c r="V5" t="n">
+        <v>301574</v>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -882,60 +999,83 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Air Terjun Coban Jahe</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>12000</v>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SAWAH GENTING</t>
+        </is>
       </c>
       <c r="H6" t="n">
-        <v>24000</v>
-      </c>
-      <c r="I6" t="inlineStr">
+        <v>12500</v>
+      </c>
+      <c r="I6" t="n">
+        <v>25500</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Warung Berkah</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Warung Jawa Sohibul Barokah</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>15000</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Warung Berkah</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>15000</v>
-      </c>
-      <c r="M6" t="n">
-        <v>75750</v>
-      </c>
-      <c r="N6" t="n">
-        <v>129.4</v>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>75250</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>28.63</v>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P6" t="n">
-        <v>291140</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>525661</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>64417</v>
+      </c>
+      <c r="V6" t="n">
+        <v>299938</v>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -963,60 +1103,83 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Air Terjun Coban Jahe</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>12000</v>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SAWAH GENTING</t>
+        </is>
       </c>
       <c r="H7" t="n">
-        <v>24000</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Warung Vespa</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>15000</v>
+        <v>12500</v>
+      </c>
+      <c r="I7" t="n">
+        <v>25500</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>Warung Berkah</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Warung Sumber Rejeki 2</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>15000</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="M7" t="n">
-        <v>75750</v>
-      </c>
-      <c r="N7" t="n">
-        <v>129.4</v>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>75250</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>28.69</v>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P7" t="n">
-        <v>291140</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>525661</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>64562</v>
+      </c>
+      <c r="V7" t="n">
+        <v>300083</v>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -1033,71 +1196,94 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hotel Asida</t>
+          <t>The New Handayani Villa's</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="E8" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Air Terjun Coban Jahe</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>OYOT ( Obyek Wisata Coban Talun )</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>12000</v>
       </c>
-      <c r="H8" t="n">
-        <v>24000</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Pawon Godong Gedang</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>15000</v>
+      <c r="I8" t="n">
+        <v>24500</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Warung Biru Lesti</t>
+          <t>Warung Berkah</t>
         </is>
       </c>
       <c r="L8" t="n">
         <v>15000</v>
       </c>
-      <c r="M8" t="n">
-        <v>75750</v>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Warung Jawa Sohibul Barokah</t>
+        </is>
       </c>
       <c r="N8" t="n">
-        <v>129.4</v>
+        <v>15000</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>Warung Sumber Rejeki 2</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>75000</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>28.74</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P8" t="n">
-        <v>291140</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>525661</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>64662</v>
+      </c>
+      <c r="V8" t="n">
+        <v>301988</v>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -1114,71 +1300,94 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hotel Asida</t>
+          <t>The New Handayani Villa's</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="E9" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Air Terjun Coban Jahe</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wisata coban talun</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>12000</v>
       </c>
-      <c r="H9" t="n">
-        <v>24000</v>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="n">
+        <v>24500</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Warung Berkah</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Warung Jawa Sohibul Barokah</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>15000</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Warung Biru Lesti</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>15000</v>
-      </c>
-      <c r="M9" t="n">
-        <v>75750</v>
-      </c>
       <c r="N9" t="n">
-        <v>129.4</v>
+        <v>15000</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>Warung Sumber Rejeki 2</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>75000</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>28.76</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P9" t="n">
-        <v>291140</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>525661</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>64712</v>
+      </c>
+      <c r="V9" t="n">
+        <v>302038</v>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -1206,60 +1415,83 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Air Terjun Coban Jahe</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Air Terjun Coban Talun</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
         <v>12000</v>
       </c>
-      <c r="H10" t="n">
-        <v>24000</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Warung Sadam</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>15000</v>
+      <c r="I10" t="n">
+        <v>24500</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>Warung Berkah</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Warung Sumber Rejeki 2</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>15000</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>15000</v>
-      </c>
-      <c r="M10" t="n">
-        <v>75750</v>
-      </c>
-      <c r="N10" t="n">
-        <v>129.4</v>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>75000</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>29.14</v>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P10" t="n">
-        <v>291140</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>525661</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>65563</v>
+      </c>
+      <c r="V10" t="n">
+        <v>299834</v>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -1287,60 +1519,83 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Air Terjun Coban Jahe</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>OYOT ( Obyek Wisata Coban Talun )</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
         <v>12000</v>
       </c>
-      <c r="H11" t="n">
-        <v>24000</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Warung Pojok Al Mustofa</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>15000</v>
+      <c r="I11" t="n">
+        <v>24500</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>Warung Sumber Rejeki 2</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Warung Berkah</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>15000</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="L11" t="n">
-        <v>15000</v>
-      </c>
-      <c r="M11" t="n">
-        <v>75750</v>
-      </c>
-      <c r="N11" t="n">
-        <v>129.4</v>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>75000</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>29.23</v>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P11" t="n">
-        <v>291140</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>525661</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>65776</v>
+      </c>
+      <c r="V11" t="n">
+        <v>300047</v>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -1368,60 +1623,83 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Air Terjun Coban Jahe</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>wisata coban talun</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
         <v>12000</v>
       </c>
-      <c r="H12" t="n">
-        <v>24000</v>
-      </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="n">
+        <v>24500</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>Warung Sumber Rejeki 2</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Warung Berkah</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>15000</v>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="L12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="M12" t="n">
-        <v>75750</v>
-      </c>
-      <c r="N12" t="n">
-        <v>129.4</v>
-      </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>75000</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>29.26</v>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P12" t="n">
-        <v>291140</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>525661</v>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>65830</v>
+      </c>
+      <c r="V12" t="n">
+        <v>300101</v>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -1449,60 +1727,83 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Air Terjun Coban Jahe</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>OYOT ( Obyek Wisata Coban Talun )</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
         <v>12000</v>
       </c>
-      <c r="H13" t="n">
-        <v>24000</v>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="n">
+        <v>24500</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>Warung Berkah</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>15000</v>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Warung Sumber Rejeki 2</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>15000</v>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="L13" t="n">
-        <v>15000</v>
-      </c>
-      <c r="M13" t="n">
-        <v>75750</v>
-      </c>
-      <c r="N13" t="n">
-        <v>129.4</v>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>75000</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>29.82</v>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P13" t="n">
-        <v>291140</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>525661</v>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="U13" t="n">
+        <v>67106</v>
+      </c>
+      <c r="V13" t="n">
+        <v>301377</v>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -1530,60 +1831,83 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Air Terjun Coban Jahe</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>wisata coban talun</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>12000</v>
       </c>
-      <c r="H14" t="n">
-        <v>24000</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Rawon Malang (Warung Biru)</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>15000</v>
+      <c r="I14" t="n">
+        <v>24500</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t>Warung Berkah</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Warung Sumber Rejeki 2</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="L14" t="n">
-        <v>15000</v>
-      </c>
-      <c r="M14" t="n">
-        <v>75750</v>
-      </c>
-      <c r="N14" t="n">
-        <v>129.4</v>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>75000</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>29.85</v>
+      </c>
+      <c r="T14" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P14" t="n">
-        <v>291140</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>525661</v>
-      </c>
-      <c r="R14" t="inlineStr">
+      <c r="U14" t="n">
+        <v>67161</v>
+      </c>
+      <c r="V14" t="n">
+        <v>301432</v>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="inlineStr">
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -1600,71 +1924,94 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hotel Asida</t>
+          <t>The New Handayani Villa's</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="E15" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Air Terjun Coban Jahe</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Air Terjun Coban Talun</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
         <v>12000</v>
       </c>
-      <c r="H15" t="n">
-        <v>24000</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Warung Pojok "Cantika"</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>15000</v>
+      <c r="I15" t="n">
+        <v>24500</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Warung Biru Lesti</t>
+          <t>Warung Berkah</t>
         </is>
       </c>
       <c r="L15" t="n">
         <v>15000</v>
       </c>
-      <c r="M15" t="n">
-        <v>75750</v>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Warung Sumber Rejeki 2</t>
+        </is>
       </c>
       <c r="N15" t="n">
-        <v>129.4</v>
+        <v>15000</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
+          <t>Warung Jawa Sohibul Barokah</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>75000</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>30.49</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P15" t="n">
-        <v>291140</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>525661</v>
-      </c>
-      <c r="R15" t="inlineStr">
+      <c r="U15" t="n">
+        <v>68600</v>
+      </c>
+      <c r="V15" t="n">
+        <v>305926</v>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="inlineStr">
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -1681,71 +2028,94 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hotel Asida</t>
+          <t>The New Handayani Villa's</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="E16" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Air Terjun Coban Jahe</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Air Terjun Coban Talun</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
         <v>12000</v>
       </c>
-      <c r="H16" t="n">
-        <v>24000</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Warung Rujak Bu Sum</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>15000</v>
+      <c r="I16" t="n">
+        <v>24500</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Warung Biru Lesti</t>
+          <t>Warung Sumber Rejeki 2</t>
         </is>
       </c>
       <c r="L16" t="n">
         <v>15000</v>
       </c>
-      <c r="M16" t="n">
-        <v>75750</v>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Warung Berkah</t>
+        </is>
       </c>
       <c r="N16" t="n">
-        <v>129.4</v>
+        <v>15000</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
+          <t>Warung Jawa Sohibul Barokah</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>75000</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>30.73</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P16" t="n">
-        <v>291140</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>525661</v>
-      </c>
-      <c r="R16" t="inlineStr">
+      <c r="U16" t="n">
+        <v>69141</v>
+      </c>
+      <c r="V16" t="n">
+        <v>306467</v>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="inlineStr">
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -1773,60 +2143,83 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>Hawai Waterpark</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>85000</v>
       </c>
-      <c r="H17" t="n">
-        <v>179100</v>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="n">
+        <v>165000</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Depot 77 Sawojajar Halalan Toyiban</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>38000</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>40250</v>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="P17" t="n">
         <v>39000</v>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Niki Kopitiam Malang</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>40250</v>
-      </c>
-      <c r="M17" t="n">
-        <v>197250</v>
-      </c>
-      <c r="N17" t="n">
-        <v>114.94</v>
-      </c>
-      <c r="O17" t="inlineStr">
+      <c r="Q17" t="n">
+        <v>196500</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>35.51</v>
+      </c>
+      <c r="T17" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P17" t="n">
-        <v>258622</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>953161</v>
-      </c>
-      <c r="R17" t="inlineStr">
+      <c r="U17" t="n">
+        <v>79897</v>
+      </c>
+      <c r="V17" t="n">
+        <v>759586</v>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="inlineStr">
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -1854,60 +2247,83 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>Hawai Waterpark</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>85000</v>
       </c>
-      <c r="H18" t="n">
-        <v>179100</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Warung Menthok Pedas Pak Nardi</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
+      <c r="I18" t="n">
+        <v>165000</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Depot 77 Sawojajar Halalan Toyiban</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>38000</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Sego Tempong by Cak Uut</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
         <v>39000</v>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Sego Tempong by Cak Uut</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>39000</v>
-      </c>
-      <c r="M18" t="n">
-        <v>197250</v>
-      </c>
-      <c r="N18" t="n">
-        <v>114.94</v>
-      </c>
       <c r="O18" t="inlineStr">
         <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>40250</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>196500</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P18" t="n">
-        <v>258622</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>953161</v>
-      </c>
-      <c r="R18" t="inlineStr">
+      <c r="U18" t="n">
+        <v>80447</v>
+      </c>
+      <c r="V18" t="n">
+        <v>760136</v>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="inlineStr">
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -1935,60 +2351,83 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>Hawai Waterpark</t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>85000</v>
       </c>
-      <c r="H19" t="n">
-        <v>179100</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Iga Bakar Saudara</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>40000</v>
+      <c r="I19" t="n">
+        <v>165000</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>40250</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Depot 77 Sawojajar Halalan Toyiban</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>38000</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="L19" t="n">
+      <c r="P19" t="n">
         <v>39000</v>
       </c>
-      <c r="M19" t="n">
-        <v>197250</v>
-      </c>
-      <c r="N19" t="n">
-        <v>114.94</v>
-      </c>
-      <c r="O19" t="inlineStr">
+      <c r="Q19" t="n">
+        <v>196500</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>38.28</v>
+      </c>
+      <c r="T19" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P19" t="n">
-        <v>258622</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>953161</v>
-      </c>
-      <c r="R19" t="inlineStr">
+      <c r="U19" t="n">
+        <v>86141</v>
+      </c>
+      <c r="V19" t="n">
+        <v>765830</v>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="inlineStr">
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -2016,60 +2455,83 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>Hawai Waterpark</t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>85000</v>
       </c>
-      <c r="H20" t="n">
-        <v>179100</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Depot Flamboyant</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>40000</v>
+      <c r="I20" t="n">
+        <v>165000</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>40250</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Kauri kitchen</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>41400</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="P20" t="n">
         <v>39000</v>
       </c>
-      <c r="M20" t="n">
-        <v>197250</v>
-      </c>
-      <c r="N20" t="n">
-        <v>114.94</v>
-      </c>
-      <c r="O20" t="inlineStr">
+      <c r="Q20" t="n">
+        <v>199900</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>40.51</v>
+      </c>
+      <c r="T20" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P20" t="n">
-        <v>258622</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>953161</v>
-      </c>
-      <c r="R20" t="inlineStr">
+      <c r="U20" t="n">
+        <v>91149</v>
+      </c>
+      <c r="V20" t="n">
+        <v>774238</v>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="inlineStr">
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -2097,60 +2559,83 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>Hawai Waterpark</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>85000</v>
       </c>
-      <c r="H21" t="n">
-        <v>179100</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Happy Durian - Durian Coffee and Eatery</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>40000</v>
+      <c r="I21" t="n">
+        <v>165000</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>40250</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Warung Wareg</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>40084</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="P21" t="n">
         <v>39000</v>
       </c>
-      <c r="M21" t="n">
-        <v>197250</v>
-      </c>
-      <c r="N21" t="n">
-        <v>114.94</v>
-      </c>
-      <c r="O21" t="inlineStr">
+      <c r="Q21" t="n">
+        <v>198584</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>41.16</v>
+      </c>
+      <c r="T21" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P21" t="n">
-        <v>258622</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>953161</v>
-      </c>
-      <c r="R21" t="inlineStr">
+      <c r="U21" t="n">
+        <v>92612</v>
+      </c>
+      <c r="V21" t="n">
+        <v>774385</v>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="inlineStr">
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -2178,60 +2663,83 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>85000</v>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>BatuPaintball</t>
+        </is>
       </c>
       <c r="H22" t="n">
-        <v>179100</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Warung Wareg</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>40084</v>
+        <v>130000</v>
+      </c>
+      <c r="I22" t="n">
+        <v>210000</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>40250</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Kauri kitchen</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>41400</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="P22" t="n">
         <v>39000</v>
       </c>
-      <c r="M22" t="n">
-        <v>197250</v>
-      </c>
-      <c r="N22" t="n">
-        <v>114.94</v>
-      </c>
-      <c r="O22" t="inlineStr">
+      <c r="Q22" t="n">
+        <v>199900</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="T22" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P22" t="n">
-        <v>258622</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>953161</v>
-      </c>
-      <c r="R22" t="inlineStr">
+      <c r="U22" t="n">
+        <v>108742</v>
+      </c>
+      <c r="V22" t="n">
+        <v>836831</v>
+      </c>
+      <c r="W22" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -2259,60 +2767,83 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>85000</v>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>BatuPaintball</t>
+        </is>
       </c>
       <c r="H23" t="n">
-        <v>179100</v>
-      </c>
-      <c r="I23" t="inlineStr">
+        <v>130000</v>
+      </c>
+      <c r="I23" t="n">
+        <v>210000</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>Niki Kopitiam Malang</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>40250</v>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Ayam bakar pak d karangploso</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>41586</v>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="P23" t="n">
         <v>39000</v>
       </c>
-      <c r="M23" t="n">
-        <v>197250</v>
-      </c>
-      <c r="N23" t="n">
-        <v>114.94</v>
-      </c>
-      <c r="O23" t="inlineStr">
+      <c r="Q23" t="n">
+        <v>200086</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>50.45</v>
+      </c>
+      <c r="T23" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P23" t="n">
-        <v>258622</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>953161</v>
-      </c>
-      <c r="R23" t="inlineStr">
+      <c r="U23" t="n">
+        <v>113516</v>
+      </c>
+      <c r="V23" t="n">
+        <v>841791</v>
+      </c>
+      <c r="W23" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -2340,60 +2871,83 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>Hawai Waterpark</t>
         </is>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>85000</v>
       </c>
-      <c r="H24" t="n">
-        <v>179100</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Rumah Makan Cairo</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>38500</v>
+      <c r="I24" t="n">
+        <v>165000</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>40250</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Ayam bakar pak d karangploso</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>41586</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="P24" t="n">
         <v>39000</v>
       </c>
-      <c r="M24" t="n">
-        <v>197250</v>
-      </c>
-      <c r="N24" t="n">
-        <v>114.94</v>
-      </c>
-      <c r="O24" t="inlineStr">
+      <c r="Q24" t="n">
+        <v>200086</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>50.83</v>
+      </c>
+      <c r="T24" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P24" t="n">
-        <v>258622</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>953161</v>
-      </c>
-      <c r="R24" t="inlineStr">
+      <c r="U24" t="n">
+        <v>114366</v>
+      </c>
+      <c r="V24" t="n">
+        <v>797641</v>
+      </c>
+      <c r="W24" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -2421,60 +2975,83 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>85000</v>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>BatuPaintball</t>
+        </is>
       </c>
       <c r="H25" t="n">
-        <v>179100</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Ayam Guling Enakko - Gondanglegi Malang</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>40690</v>
+        <v>130000</v>
+      </c>
+      <c r="I25" t="n">
+        <v>210000</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>40250</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Warung Wareg</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>40084</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="L25" t="n">
+      <c r="P25" t="n">
         <v>39000</v>
       </c>
-      <c r="M25" t="n">
-        <v>197250</v>
-      </c>
-      <c r="N25" t="n">
-        <v>114.94</v>
-      </c>
-      <c r="O25" t="inlineStr">
+      <c r="Q25" t="n">
+        <v>198584</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>51.45</v>
+      </c>
+      <c r="T25" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P25" t="n">
-        <v>258622</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>953161</v>
-      </c>
-      <c r="R25" t="inlineStr">
+      <c r="U25" t="n">
+        <v>115765</v>
+      </c>
+      <c r="V25" t="n">
+        <v>842538</v>
+      </c>
+      <c r="W25" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -2502,60 +3079,83 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>85000</v>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>BatuPaintball</t>
+        </is>
       </c>
       <c r="H26" t="n">
-        <v>179100</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Depot 77 Sawojajar Halalan Toyiban</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>38000</v>
+        <v>130000</v>
+      </c>
+      <c r="I26" t="n">
+        <v>210000</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>40250</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Iga Bakar Saudara</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="P26" t="n">
         <v>39000</v>
       </c>
-      <c r="M26" t="n">
-        <v>197250</v>
-      </c>
-      <c r="N26" t="n">
-        <v>114.94</v>
-      </c>
-      <c r="O26" t="inlineStr">
+      <c r="Q26" t="n">
+        <v>198500</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>52.58</v>
+      </c>
+      <c r="T26" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P26" t="n">
-        <v>258622</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>953161</v>
-      </c>
-      <c r="R26" t="inlineStr">
+      <c r="U26" t="n">
+        <v>118309</v>
+      </c>
+      <c r="V26" t="n">
+        <v>844998</v>
+      </c>
+      <c r="W26" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -2583,60 +3183,83 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>85000</v>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>BatuPaintball</t>
+        </is>
       </c>
       <c r="H27" t="n">
-        <v>179100</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Gubug asape Asapan dan bakaran</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>37800</v>
+        <v>130000</v>
+      </c>
+      <c r="I27" t="n">
+        <v>210000</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t>Depot 77 Sawojajar Halalan Toyiban</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>38000</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>40250</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="L27" t="n">
+      <c r="P27" t="n">
         <v>39000</v>
       </c>
-      <c r="M27" t="n">
-        <v>197250</v>
-      </c>
-      <c r="N27" t="n">
-        <v>114.94</v>
-      </c>
-      <c r="O27" t="inlineStr">
+      <c r="Q27" t="n">
+        <v>196500</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="T27" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P27" t="n">
-        <v>258622</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>953161</v>
-      </c>
-      <c r="R27" t="inlineStr">
+      <c r="U27" t="n">
+        <v>123080</v>
+      </c>
+      <c r="V27" t="n">
+        <v>847769</v>
+      </c>
+      <c r="W27" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -2664,60 +3287,83 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>85000</v>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>BatuPaintball</t>
+        </is>
       </c>
       <c r="H28" t="n">
-        <v>179100</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Warung Wisata</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>41337</v>
+        <v>130000</v>
+      </c>
+      <c r="I28" t="n">
+        <v>210000</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>40250</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Gubug asape Asapan dan bakaran</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>37800</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="L28" t="n">
+      <c r="P28" t="n">
         <v>39000</v>
       </c>
-      <c r="M28" t="n">
-        <v>197250</v>
-      </c>
-      <c r="N28" t="n">
-        <v>114.94</v>
-      </c>
-      <c r="O28" t="inlineStr">
+      <c r="Q28" t="n">
+        <v>196300</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="T28" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P28" t="n">
-        <v>258622</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>953161</v>
-      </c>
-      <c r="R28" t="inlineStr">
+      <c r="U28" t="n">
+        <v>126318</v>
+      </c>
+      <c r="V28" t="n">
+        <v>850807</v>
+      </c>
+      <c r="W28" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -2745,60 +3391,83 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>85000</v>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>BatuPaintball</t>
+        </is>
       </c>
       <c r="H29" t="n">
-        <v>179100</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Wisata Warung Wareg</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>41337</v>
+        <v>130000</v>
+      </c>
+      <c r="I29" t="n">
+        <v>210000</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>40250</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Depot 77 Sawojajar Halalan Toyiban</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>38000</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="L29" t="n">
+      <c r="P29" t="n">
         <v>39000</v>
       </c>
-      <c r="M29" t="n">
-        <v>197250</v>
-      </c>
-      <c r="N29" t="n">
-        <v>114.94</v>
-      </c>
-      <c r="O29" t="inlineStr">
+      <c r="Q29" t="n">
+        <v>196500</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="S29" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="T29" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P29" t="n">
-        <v>258622</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>953161</v>
-      </c>
-      <c r="R29" t="inlineStr">
+      <c r="U29" t="n">
+        <v>129324</v>
+      </c>
+      <c r="V29" t="n">
+        <v>854013</v>
+      </c>
+      <c r="W29" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -2826,60 +3495,83 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>85000</v>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>BatuPaintball</t>
+        </is>
       </c>
       <c r="H30" t="n">
-        <v>179100</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Kauri kitchen</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>41400</v>
+        <v>130000</v>
+      </c>
+      <c r="I30" t="n">
+        <v>210000</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t>Depot 77 Sawojajar Halalan Toyiban</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>38000</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>39000</v>
       </c>
-      <c r="M30" t="n">
-        <v>197250</v>
-      </c>
-      <c r="N30" t="n">
-        <v>114.94</v>
-      </c>
       <c r="O30" t="inlineStr">
         <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>40250</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>196500</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P30" t="n">
-        <v>258622</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>953161</v>
-      </c>
-      <c r="R30" t="inlineStr">
+      <c r="U30" t="n">
+        <v>129425</v>
+      </c>
+      <c r="V30" t="n">
+        <v>854114</v>
+      </c>
+      <c r="W30" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -2907,60 +3599,83 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>Hawai Waterpark</t>
         </is>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>85000</v>
       </c>
-      <c r="H31" t="n">
-        <v>179100</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Ayam bakar pak d karangploso</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>41586</v>
+      <c r="I31" t="n">
+        <v>165000</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>40250</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Happy Durian - Durian Coffee and Eatery</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="L31" t="n">
+      <c r="P31" t="n">
         <v>39000</v>
       </c>
-      <c r="M31" t="n">
-        <v>197250</v>
-      </c>
-      <c r="N31" t="n">
-        <v>114.94</v>
-      </c>
-      <c r="O31" t="inlineStr">
+      <c r="Q31" t="n">
+        <v>198500</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>59.87</v>
+      </c>
+      <c r="T31" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="P31" t="n">
-        <v>258622</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>953161</v>
-      </c>
-      <c r="R31" t="inlineStr">
+      <c r="U31" t="n">
+        <v>134701</v>
+      </c>
+      <c r="V31" t="n">
+        <v>816390</v>
+      </c>
+      <c r="W31" t="inlineStr">
         <is>
           <t>N/A (Flexible Exploration)</t>
         </is>
       </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="inlineStr">
         <is>
           <t>FLEXIBLE EXPLORATION</t>
         </is>
@@ -3302,77 +4017,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>The New Handayani Villa's</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Hotel Asida</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Hotel Asida</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>The New Handayani Villa's</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Hotel Asida</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Hotel Asida</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>The New Handayani Villa's</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>The New Handayani Villa's</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>Hotel Asida</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Hotel Asida</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Hotel Asida</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Hotel Asida</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Hotel Asida</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Hotel Asida</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Hotel Asida</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Hotel Asida</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Hotel Asida</t>
-        </is>
-      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Hotel Asida</t>
+          <t>The New Handayani Villa's</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hotel Asida</t>
+          <t>The New Handayani Villa's</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -3458,7 +4173,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="C4" t="n">
         <v>134771</v>
@@ -3467,7 +4182,7 @@
         <v>134771</v>
       </c>
       <c r="E4" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="F4" t="n">
         <v>134771</v>
@@ -3476,10 +4191,10 @@
         <v>134771</v>
       </c>
       <c r="H4" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="I4" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="J4" t="n">
         <v>134771</v>
@@ -3497,10 +4212,10 @@
         <v>134771</v>
       </c>
       <c r="O4" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="P4" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="Q4" t="n">
         <v>318189</v>
@@ -3561,147 +4276,147 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>SAWAH GENTING</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>Air Terjun Coban Talun</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SAWAH GENTING</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SAWAH GENTING</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SAWAH GENTING</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>OYOT ( Obyek Wisata Coban Talun )</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>wisata coban talun</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>Air Terjun Coban Talun</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>OYOT ( Obyek Wisata Coban Talun )</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>wisata coban talun</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>OYOT ( Obyek Wisata Coban Talun )</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>wisata coban talun</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>Air Terjun Coban Talun</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Air Terjun Coban Talun</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Air Terjun Coban Talun</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Air Terjun Coban Talun</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Air Terjun Coban Talun</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Air Terjun Coban Talun</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Air Terjun Coban Talun</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Air Terjun Coban Talun</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Air Terjun Coban Talun</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Air Terjun Coban Talun</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Air Terjun Coban Talun</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Air Terjun Coban Talun</t>
-        </is>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Lampion &amp; Dinosaurus Park</t>
+          <t>Hawai Waterpark</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Lampion &amp; Dinosaurus Park</t>
+          <t>Hawai Waterpark</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Lampion &amp; Dinosaurus Park</t>
+          <t>Hawai Waterpark</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Lampion &amp; Dinosaurus Park</t>
+          <t>Hawai Waterpark</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Lampion &amp; Dinosaurus Park</t>
+          <t>Hawai Waterpark</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Lampion &amp; Dinosaurus Park</t>
+          <t>BatuPaintball</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Lampion &amp; Dinosaurus Park</t>
+          <t>BatuPaintball</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Lampion &amp; Dinosaurus Park</t>
+          <t>Hawai Waterpark</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Lampion &amp; Dinosaurus Park</t>
+          <t>BatuPaintball</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Lampion &amp; Dinosaurus Park</t>
+          <t>BatuPaintball</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Lampion &amp; Dinosaurus Park</t>
+          <t>BatuPaintball</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Lampion &amp; Dinosaurus Park</t>
+          <t>BatuPaintball</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Lampion &amp; Dinosaurus Park</t>
+          <t>BatuPaintball</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Lampion &amp; Dinosaurus Park</t>
+          <t>BatuPaintball</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Lampion &amp; Dinosaurus Park</t>
+          <t>Hawai Waterpark</t>
         </is>
       </c>
     </row>
@@ -3715,19 +4430,19 @@
         <v>12000</v>
       </c>
       <c r="C6" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="D6" t="n">
         <v>12000</v>
       </c>
       <c r="E6" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="F6" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="G6" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="H6" t="n">
         <v>12000</v>
@@ -3757,49 +4472,49 @@
         <v>12000</v>
       </c>
       <c r="Q6" t="n">
-        <v>90000</v>
+        <v>85000</v>
       </c>
       <c r="R6" t="n">
-        <v>90000</v>
+        <v>85000</v>
       </c>
       <c r="S6" t="n">
-        <v>90000</v>
+        <v>85000</v>
       </c>
       <c r="T6" t="n">
-        <v>90000</v>
+        <v>85000</v>
       </c>
       <c r="U6" t="n">
-        <v>90000</v>
+        <v>85000</v>
       </c>
       <c r="V6" t="n">
-        <v>90000</v>
+        <v>130000</v>
       </c>
       <c r="W6" t="n">
-        <v>90000</v>
+        <v>130000</v>
       </c>
       <c r="X6" t="n">
-        <v>90000</v>
+        <v>85000</v>
       </c>
       <c r="Y6" t="n">
-        <v>90000</v>
+        <v>130000</v>
       </c>
       <c r="Z6" t="n">
-        <v>90000</v>
+        <v>130000</v>
       </c>
       <c r="AA6" t="n">
-        <v>90000</v>
+        <v>130000</v>
       </c>
       <c r="AB6" t="n">
-        <v>90000</v>
+        <v>130000</v>
       </c>
       <c r="AC6" t="n">
-        <v>90000</v>
+        <v>130000</v>
       </c>
       <c r="AD6" t="n">
-        <v>90000</v>
+        <v>130000</v>
       </c>
       <c r="AE6" t="n">
-        <v>90000</v>
+        <v>85000</v>
       </c>
     </row>
     <row r="7">
@@ -3815,142 +4530,142 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Warung Sumber Rejeki 2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Warung Sumber Rejeki 2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Warung Berkah</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Warung Berkah</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Warung Berkah</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Warung Berkah</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Warung Berkah</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Warung Berkah</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Warung Sumber Rejeki 2</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Warung Sumber Rejeki 2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Warung Berkah</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Warung Berkah</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Warung Berkah</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Warung Berkah</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Warung Berkah</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Warung Berkah</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Warung Berkah</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Warung Berkah</t>
+          <t>Warung Sumber Rejeki 2</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>Depot 77 Sawojajar Halalan Toyiban</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Depot 77 Sawojajar Halalan Toyiban</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
           <t>Niki Kopitiam Malang</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Niki Kopitiam Malang</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Niki Kopitiam Malang</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Niki Kopitiam Malang</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Niki Kopitiam Malang</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Niki Kopitiam Malang</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Niki Kopitiam Malang</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>Niki Kopitiam Malang</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Depot 77 Sawojajar Halalan Toyiban</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Niki Kopitiam Malang</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Niki Kopitiam Malang</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Niki Kopitiam Malang</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Niki Kopitiam Malang</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Niki Kopitiam Malang</t>
-        </is>
-      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Niki Kopitiam Malang</t>
+          <t>Depot 77 Sawojajar Halalan Toyiban</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -4011,10 +4726,10 @@
         <v>15000</v>
       </c>
       <c r="Q8" t="n">
-        <v>40250</v>
+        <v>38000</v>
       </c>
       <c r="R8" t="n">
-        <v>40250</v>
+        <v>38000</v>
       </c>
       <c r="S8" t="n">
         <v>40250</v>
@@ -4041,7 +4756,7 @@
         <v>40250</v>
       </c>
       <c r="AA8" t="n">
-        <v>40250</v>
+        <v>38000</v>
       </c>
       <c r="AB8" t="n">
         <v>40250</v>
@@ -4050,7 +4765,7 @@
         <v>40250</v>
       </c>
       <c r="AD8" t="n">
-        <v>40250</v>
+        <v>38000</v>
       </c>
       <c r="AE8" t="n">
         <v>40250</v>
@@ -4064,152 +4779,152 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Warung Bu Erni</t>
+          <t>Warung Jawa Sohibul Barokah</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Warung Bu Erni</t>
+          <t>Warung Berkah</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Warung Bu Erni</t>
+          <t>Warung Berkah</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Warung Bu Erni</t>
+          <t>Warung Jawa Sohibul Barokah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Warung Bu Erni</t>
+          <t>Warung Jawa Sohibul Barokah</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Warung Bu Erni</t>
+          <t>Warung Sumber Rejeki 2</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Warung Bu Erni</t>
+          <t>Warung Jawa Sohibul Barokah</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Warung Bu Erni</t>
+          <t>Warung Jawa Sohibul Barokah</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Warung Bu Erni</t>
+          <t>Warung Sumber Rejeki 2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Warung Bu Erni</t>
+          <t>Warung Berkah</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Warung Bu Erni</t>
+          <t>Warung Berkah</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Warung Bu Erni</t>
+          <t>Warung Sumber Rejeki 2</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Warung Bu Erni</t>
+          <t>Warung Sumber Rejeki 2</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Warung Bu Erni</t>
+          <t>Warung Sumber Rejeki 2</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Warung Bu Erni</t>
+          <t>Warung Berkah</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Warung Menthok Pedas Pak Nardi</t>
+          <t>Niki Kopitiam Malang</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Warung Menthok Pedas Pak Nardi</t>
+          <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Warung Menthok Pedas Pak Nardi</t>
+          <t>Depot 77 Sawojajar Halalan Toyiban</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Warung Menthok Pedas Pak Nardi</t>
+          <t>Kauri kitchen</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Warung Menthok Pedas Pak Nardi</t>
+          <t>Warung Wareg</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Warung Menthok Pedas Pak Nardi</t>
+          <t>Kauri kitchen</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Warung Menthok Pedas Pak Nardi</t>
+          <t>Ayam bakar pak d karangploso</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Warung Menthok Pedas Pak Nardi</t>
+          <t>Ayam bakar pak d karangploso</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Warung Menthok Pedas Pak Nardi</t>
+          <t>Warung Wareg</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Warung Menthok Pedas Pak Nardi</t>
+          <t>Iga Bakar Saudara</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Warung Menthok Pedas Pak Nardi</t>
+          <t>Niki Kopitiam Malang</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Warung Menthok Pedas Pak Nardi</t>
+          <t>Gubug asape Asapan dan bakaran</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Warung Menthok Pedas Pak Nardi</t>
+          <t>Depot 77 Sawojajar Halalan Toyiban</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Warung Menthok Pedas Pak Nardi</t>
+          <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>Warung Menthok Pedas Pak Nardi</t>
+          <t>Happy Durian - Durian Coffee and Eatery</t>
         </is>
       </c>
     </row>
@@ -4220,94 +4935,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15350</v>
+        <v>15000</v>
       </c>
       <c r="C10" t="n">
-        <v>15350</v>
+        <v>15000</v>
       </c>
       <c r="D10" t="n">
-        <v>15350</v>
+        <v>15000</v>
       </c>
       <c r="E10" t="n">
-        <v>15350</v>
+        <v>15000</v>
       </c>
       <c r="F10" t="n">
-        <v>15350</v>
+        <v>15000</v>
       </c>
       <c r="G10" t="n">
-        <v>15350</v>
+        <v>15000</v>
       </c>
       <c r="H10" t="n">
-        <v>15350</v>
+        <v>15000</v>
       </c>
       <c r="I10" t="n">
-        <v>15350</v>
+        <v>15000</v>
       </c>
       <c r="J10" t="n">
-        <v>15350</v>
+        <v>15000</v>
       </c>
       <c r="K10" t="n">
-        <v>15350</v>
+        <v>15000</v>
       </c>
       <c r="L10" t="n">
-        <v>15350</v>
+        <v>15000</v>
       </c>
       <c r="M10" t="n">
-        <v>15350</v>
+        <v>15000</v>
       </c>
       <c r="N10" t="n">
-        <v>15350</v>
+        <v>15000</v>
       </c>
       <c r="O10" t="n">
-        <v>15350</v>
+        <v>15000</v>
       </c>
       <c r="P10" t="n">
-        <v>15350</v>
+        <v>15000</v>
       </c>
       <c r="Q10" t="n">
-        <v>39000</v>
+        <v>40250</v>
       </c>
       <c r="R10" t="n">
         <v>39000</v>
       </c>
       <c r="S10" t="n">
-        <v>39000</v>
+        <v>38000</v>
       </c>
       <c r="T10" t="n">
-        <v>39000</v>
+        <v>41400</v>
       </c>
       <c r="U10" t="n">
-        <v>39000</v>
+        <v>40084</v>
       </c>
       <c r="V10" t="n">
-        <v>39000</v>
+        <v>41400</v>
       </c>
       <c r="W10" t="n">
-        <v>39000</v>
+        <v>41586</v>
       </c>
       <c r="X10" t="n">
-        <v>39000</v>
+        <v>41586</v>
       </c>
       <c r="Y10" t="n">
-        <v>39000</v>
+        <v>40084</v>
       </c>
       <c r="Z10" t="n">
-        <v>39000</v>
+        <v>40000</v>
       </c>
       <c r="AA10" t="n">
-        <v>39000</v>
+        <v>40250</v>
       </c>
       <c r="AB10" t="n">
-        <v>39000</v>
+        <v>37800</v>
       </c>
       <c r="AC10" t="n">
-        <v>39000</v>
+        <v>38000</v>
       </c>
       <c r="AD10" t="n">
         <v>39000</v>
       </c>
       <c r="AE10" t="n">
-        <v>39000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="11">
@@ -4318,77 +5033,77 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>Warung Sumber Rejeki 2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Warung Sumber Rejeki 2</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Warung Sumber Rejeki 2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Warung Sumber Rejeki 2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Warung Biru Lesti</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Warung Biru Lesti</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Warung Biru Lesti</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Warung Biru Lesti</t>
-        </is>
-      </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Warung Biru Lesti</t>
+          <t>Warung Jawa Sohibul Barokah</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Warung Biru Lesti</t>
+          <t>Warung Jawa Sohibul Barokah</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -4398,67 +5113,67 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Sego Tempong by Cak Uut</t>
-        </is>
-      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>Sego Tempong by Cak Uut</t>
+          <t>Niki Kopitiam Malang</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -4522,7 +5237,7 @@
         <v>39000</v>
       </c>
       <c r="R12" t="n">
-        <v>39000</v>
+        <v>40250</v>
       </c>
       <c r="S12" t="n">
         <v>39000</v>
@@ -4558,7 +5273,7 @@
         <v>39000</v>
       </c>
       <c r="AD12" t="n">
-        <v>39000</v>
+        <v>40250</v>
       </c>
       <c r="AE12" t="n">
         <v>39000</v>
@@ -4571,7 +5286,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="C13" t="n">
         <v>134771</v>
@@ -4580,7 +5295,7 @@
         <v>134771</v>
       </c>
       <c r="E13" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="F13" t="n">
         <v>134771</v>
@@ -4589,10 +5304,10 @@
         <v>134771</v>
       </c>
       <c r="H13" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="I13" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="J13" t="n">
         <v>134771</v>
@@ -4610,10 +5325,10 @@
         <v>134771</v>
       </c>
       <c r="O13" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="P13" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="Q13" t="n">
         <v>318189</v>
@@ -4671,19 +5386,19 @@
         <v>12000</v>
       </c>
       <c r="C14" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="D14" t="n">
         <v>12000</v>
       </c>
       <c r="E14" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="F14" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="G14" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="H14" t="n">
         <v>12000</v>
@@ -4713,49 +5428,49 @@
         <v>12000</v>
       </c>
       <c r="Q14" t="n">
-        <v>90000</v>
+        <v>85000</v>
       </c>
       <c r="R14" t="n">
-        <v>90000</v>
+        <v>85000</v>
       </c>
       <c r="S14" t="n">
-        <v>90000</v>
+        <v>85000</v>
       </c>
       <c r="T14" t="n">
-        <v>90000</v>
+        <v>85000</v>
       </c>
       <c r="U14" t="n">
-        <v>90000</v>
+        <v>85000</v>
       </c>
       <c r="V14" t="n">
-        <v>90000</v>
+        <v>130000</v>
       </c>
       <c r="W14" t="n">
-        <v>90000</v>
+        <v>130000</v>
       </c>
       <c r="X14" t="n">
-        <v>90000</v>
+        <v>85000</v>
       </c>
       <c r="Y14" t="n">
-        <v>90000</v>
+        <v>130000</v>
       </c>
       <c r="Z14" t="n">
-        <v>90000</v>
+        <v>130000</v>
       </c>
       <c r="AA14" t="n">
-        <v>90000</v>
+        <v>130000</v>
       </c>
       <c r="AB14" t="n">
-        <v>90000</v>
+        <v>130000</v>
       </c>
       <c r="AC14" t="n">
-        <v>90000</v>
+        <v>130000</v>
       </c>
       <c r="AD14" t="n">
-        <v>90000</v>
+        <v>130000</v>
       </c>
       <c r="AE14" t="n">
-        <v>90000</v>
+        <v>85000</v>
       </c>
     </row>
     <row r="15">
@@ -4765,94 +5480,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>45350</v>
+        <v>45000</v>
       </c>
       <c r="C15" t="n">
-        <v>45350</v>
+        <v>45000</v>
       </c>
       <c r="D15" t="n">
-        <v>45350</v>
+        <v>45000</v>
       </c>
       <c r="E15" t="n">
-        <v>45350</v>
+        <v>45000</v>
       </c>
       <c r="F15" t="n">
-        <v>45350</v>
+        <v>45000</v>
       </c>
       <c r="G15" t="n">
-        <v>45350</v>
+        <v>45000</v>
       </c>
       <c r="H15" t="n">
-        <v>45350</v>
+        <v>45000</v>
       </c>
       <c r="I15" t="n">
-        <v>45350</v>
+        <v>45000</v>
       </c>
       <c r="J15" t="n">
-        <v>45350</v>
+        <v>45000</v>
       </c>
       <c r="K15" t="n">
-        <v>45350</v>
+        <v>45000</v>
       </c>
       <c r="L15" t="n">
-        <v>45350</v>
+        <v>45000</v>
       </c>
       <c r="M15" t="n">
-        <v>45350</v>
+        <v>45000</v>
       </c>
       <c r="N15" t="n">
-        <v>45350</v>
+        <v>45000</v>
       </c>
       <c r="O15" t="n">
-        <v>45350</v>
+        <v>45000</v>
       </c>
       <c r="P15" t="n">
-        <v>45350</v>
+        <v>45000</v>
       </c>
       <c r="Q15" t="n">
-        <v>118250</v>
+        <v>117250</v>
       </c>
       <c r="R15" t="n">
-        <v>118250</v>
+        <v>117250</v>
       </c>
       <c r="S15" t="n">
-        <v>118250</v>
+        <v>117250</v>
       </c>
       <c r="T15" t="n">
-        <v>118250</v>
+        <v>120650</v>
       </c>
       <c r="U15" t="n">
-        <v>118250</v>
+        <v>119334</v>
       </c>
       <c r="V15" t="n">
-        <v>118250</v>
+        <v>120650</v>
       </c>
       <c r="W15" t="n">
-        <v>118250</v>
+        <v>120836</v>
       </c>
       <c r="X15" t="n">
-        <v>118250</v>
+        <v>120836</v>
       </c>
       <c r="Y15" t="n">
-        <v>118250</v>
+        <v>119334</v>
       </c>
       <c r="Z15" t="n">
-        <v>118250</v>
+        <v>119250</v>
       </c>
       <c r="AA15" t="n">
-        <v>118250</v>
+        <v>117250</v>
       </c>
       <c r="AB15" t="n">
-        <v>118250</v>
+        <v>117050</v>
       </c>
       <c r="AC15" t="n">
-        <v>118250</v>
+        <v>117250</v>
       </c>
       <c r="AD15" t="n">
-        <v>118250</v>
+        <v>117250</v>
       </c>
       <c r="AE15" t="n">
-        <v>118250</v>
+        <v>119250</v>
       </c>
     </row>
     <row r="16">
@@ -4862,94 +5577,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>145570</v>
+        <v>31579</v>
       </c>
       <c r="C16" t="n">
-        <v>145570</v>
+        <v>31616</v>
       </c>
       <c r="D16" t="n">
-        <v>145570</v>
+        <v>32116</v>
       </c>
       <c r="E16" t="n">
-        <v>145570</v>
+        <v>32124</v>
       </c>
       <c r="F16" t="n">
-        <v>145570</v>
+        <v>32208</v>
       </c>
       <c r="G16" t="n">
-        <v>145570</v>
+        <v>32281</v>
       </c>
       <c r="H16" t="n">
-        <v>145570</v>
+        <v>32331</v>
       </c>
       <c r="I16" t="n">
-        <v>145570</v>
+        <v>32356</v>
       </c>
       <c r="J16" t="n">
-        <v>145570</v>
+        <v>32782</v>
       </c>
       <c r="K16" t="n">
-        <v>145570</v>
+        <v>32888</v>
       </c>
       <c r="L16" t="n">
-        <v>145570</v>
+        <v>32915</v>
       </c>
       <c r="M16" t="n">
-        <v>145570</v>
+        <v>33553</v>
       </c>
       <c r="N16" t="n">
-        <v>145570</v>
+        <v>33580</v>
       </c>
       <c r="O16" t="n">
-        <v>145570</v>
+        <v>34300</v>
       </c>
       <c r="P16" t="n">
-        <v>145570</v>
+        <v>34570</v>
       </c>
       <c r="Q16" t="n">
-        <v>129311</v>
+        <v>39948</v>
       </c>
       <c r="R16" t="n">
-        <v>129311</v>
+        <v>40224</v>
       </c>
       <c r="S16" t="n">
-        <v>129311</v>
+        <v>43070</v>
       </c>
       <c r="T16" t="n">
-        <v>129311</v>
+        <v>45574</v>
       </c>
       <c r="U16" t="n">
-        <v>129311</v>
+        <v>46306</v>
       </c>
       <c r="V16" t="n">
-        <v>129311</v>
+        <v>54371</v>
       </c>
       <c r="W16" t="n">
-        <v>129311</v>
+        <v>56758</v>
       </c>
       <c r="X16" t="n">
-        <v>129311</v>
+        <v>57183</v>
       </c>
       <c r="Y16" t="n">
-        <v>129311</v>
+        <v>57882</v>
       </c>
       <c r="Z16" t="n">
-        <v>129311</v>
+        <v>59154</v>
       </c>
       <c r="AA16" t="n">
-        <v>129311</v>
+        <v>61540</v>
       </c>
       <c r="AB16" t="n">
-        <v>129311</v>
+        <v>63159</v>
       </c>
       <c r="AC16" t="n">
-        <v>129311</v>
+        <v>64662</v>
       </c>
       <c r="AD16" t="n">
-        <v>129311</v>
+        <v>64712</v>
       </c>
       <c r="AE16" t="n">
-        <v>129311</v>
+        <v>67350</v>
       </c>
     </row>
     <row r="17">
@@ -4962,40 +5677,40 @@
         <v>7.07</v>
       </c>
       <c r="C17" t="n">
-        <v>7.07</v>
+        <v>3.37</v>
       </c>
       <c r="D17" t="n">
         <v>7.07</v>
       </c>
       <c r="E17" t="n">
-        <v>7.07</v>
+        <v>3.86</v>
       </c>
       <c r="F17" t="n">
-        <v>7.07</v>
+        <v>3.86</v>
       </c>
       <c r="G17" t="n">
-        <v>7.07</v>
+        <v>3.86</v>
       </c>
       <c r="H17" t="n">
-        <v>7.07</v>
+        <v>7.41</v>
       </c>
       <c r="I17" t="n">
-        <v>7.07</v>
+        <v>7.42</v>
       </c>
       <c r="J17" t="n">
         <v>7.07</v>
       </c>
       <c r="K17" t="n">
-        <v>7.07</v>
+        <v>7.41</v>
       </c>
       <c r="L17" t="n">
-        <v>7.07</v>
+        <v>7.42</v>
       </c>
       <c r="M17" t="n">
-        <v>7.07</v>
+        <v>7.41</v>
       </c>
       <c r="N17" t="n">
-        <v>7.07</v>
+        <v>7.42</v>
       </c>
       <c r="O17" t="n">
         <v>7.07</v>
@@ -5004,49 +5719,49 @@
         <v>7.07</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.640000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>9.640000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>9.640000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>9.640000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>9.640000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>9.640000000000001</v>
+        <v>15.6</v>
       </c>
       <c r="W17" t="n">
-        <v>9.640000000000001</v>
+        <v>15.6</v>
       </c>
       <c r="X17" t="n">
-        <v>9.640000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y17" t="n">
-        <v>9.640000000000001</v>
+        <v>15.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>9.640000000000001</v>
+        <v>15.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>9.640000000000001</v>
+        <v>22.26</v>
       </c>
       <c r="AB17" t="n">
-        <v>9.640000000000001</v>
+        <v>15.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.640000000000001</v>
+        <v>15.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>9.640000000000001</v>
+        <v>22.26</v>
       </c>
       <c r="AE17" t="n">
-        <v>9.640000000000001</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -5056,94 +5771,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10.34</v>
+        <v>4.65</v>
       </c>
       <c r="C18" t="n">
-        <v>10.34</v>
+        <v>3.86</v>
       </c>
       <c r="D18" t="n">
-        <v>10.34</v>
+        <v>7.07</v>
       </c>
       <c r="E18" t="n">
-        <v>10.34</v>
+        <v>0.85</v>
       </c>
       <c r="F18" t="n">
-        <v>10.34</v>
+        <v>0.85</v>
       </c>
       <c r="G18" t="n">
-        <v>10.34</v>
+        <v>3.37</v>
       </c>
       <c r="H18" t="n">
-        <v>10.34</v>
+        <v>4.98</v>
       </c>
       <c r="I18" t="n">
-        <v>10.34</v>
+        <v>4.99</v>
       </c>
       <c r="J18" t="n">
-        <v>10.34</v>
+        <v>7.07</v>
       </c>
       <c r="K18" t="n">
-        <v>10.34</v>
+        <v>7.41</v>
       </c>
       <c r="L18" t="n">
-        <v>10.34</v>
+        <v>7.42</v>
       </c>
       <c r="M18" t="n">
-        <v>10.34</v>
+        <v>7.41</v>
       </c>
       <c r="N18" t="n">
-        <v>10.34</v>
+        <v>7.42</v>
       </c>
       <c r="O18" t="n">
-        <v>10.34</v>
+        <v>7.07</v>
       </c>
       <c r="P18" t="n">
-        <v>10.34</v>
+        <v>7.07</v>
       </c>
       <c r="Q18" t="n">
-        <v>46.29</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R18" t="n">
-        <v>46.29</v>
+        <v>9.94</v>
       </c>
       <c r="S18" t="n">
-        <v>46.29</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>46.29</v>
+        <v>11.02</v>
       </c>
       <c r="U18" t="n">
-        <v>46.29</v>
+        <v>6.03</v>
       </c>
       <c r="V18" t="n">
-        <v>46.29</v>
+        <v>12.93</v>
       </c>
       <c r="W18" t="n">
-        <v>46.29</v>
+        <v>5.22</v>
       </c>
       <c r="X18" t="n">
-        <v>46.29</v>
+        <v>11.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>46.29</v>
+        <v>10.42</v>
       </c>
       <c r="Z18" t="n">
-        <v>46.29</v>
+        <v>2.72</v>
       </c>
       <c r="AA18" t="n">
-        <v>46.29</v>
+        <v>15.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>46.29</v>
+        <v>4.17</v>
       </c>
       <c r="AC18" t="n">
-        <v>46.29</v>
+        <v>22.26</v>
       </c>
       <c r="AD18" t="n">
-        <v>46.29</v>
+        <v>18.42</v>
       </c>
       <c r="AE18" t="n">
-        <v>46.29</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="19">
@@ -5153,94 +5868,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.64</v>
+        <v>1.72</v>
       </c>
       <c r="C19" t="n">
-        <v>5.64</v>
+        <v>3.5</v>
       </c>
       <c r="D19" t="n">
-        <v>5.64</v>
+        <v>3.5</v>
       </c>
       <c r="E19" t="n">
-        <v>5.64</v>
+        <v>1.72</v>
       </c>
       <c r="F19" t="n">
-        <v>5.64</v>
+        <v>6.55</v>
       </c>
       <c r="G19" t="n">
-        <v>5.64</v>
+        <v>4.1</v>
       </c>
       <c r="H19" t="n">
-        <v>5.64</v>
+        <v>1.72</v>
       </c>
       <c r="I19" t="n">
-        <v>5.64</v>
+        <v>1.72</v>
       </c>
       <c r="J19" t="n">
-        <v>5.64</v>
+        <v>4.1</v>
       </c>
       <c r="K19" t="n">
-        <v>5.64</v>
+        <v>3.5</v>
       </c>
       <c r="L19" t="n">
-        <v>5.64</v>
+        <v>3.5</v>
       </c>
       <c r="M19" t="n">
-        <v>5.64</v>
+        <v>4.1</v>
       </c>
       <c r="N19" t="n">
-        <v>5.64</v>
+        <v>4.1</v>
       </c>
       <c r="O19" t="n">
-        <v>5.64</v>
+        <v>4.34</v>
       </c>
       <c r="P19" t="n">
-        <v>5.64</v>
+        <v>4.58</v>
       </c>
       <c r="Q19" t="n">
-        <v>35.64</v>
+        <v>3.37</v>
       </c>
       <c r="R19" t="n">
-        <v>35.64</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>35.64</v>
+        <v>6.15</v>
       </c>
       <c r="T19" t="n">
-        <v>35.64</v>
+        <v>6.33</v>
       </c>
       <c r="U19" t="n">
-        <v>35.64</v>
+        <v>11.97</v>
       </c>
       <c r="V19" t="n">
-        <v>35.64</v>
+        <v>6.33</v>
       </c>
       <c r="W19" t="n">
-        <v>35.64</v>
+        <v>16.16</v>
       </c>
       <c r="X19" t="n">
-        <v>35.64</v>
+        <v>16.16</v>
       </c>
       <c r="Y19" t="n">
-        <v>35.64</v>
+        <v>11.97</v>
       </c>
       <c r="Z19" t="n">
-        <v>35.64</v>
+        <v>20.79</v>
       </c>
       <c r="AA19" t="n">
-        <v>35.64</v>
+        <v>3.37</v>
       </c>
       <c r="AB19" t="n">
-        <v>35.64</v>
+        <v>22.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>35.64</v>
+        <v>6.15</v>
       </c>
       <c r="AD19" t="n">
-        <v>35.64</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
-        <v>35.64</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -5250,7 +5965,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1</v>
+        <v>4.34</v>
       </c>
       <c r="C20" t="n">
         <v>1.1</v>
@@ -5259,7 +5974,7 @@
         <v>1.1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1</v>
+        <v>4.34</v>
       </c>
       <c r="F20" t="n">
         <v>1.1</v>
@@ -5268,10 +5983,10 @@
         <v>1.1</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1</v>
+        <v>4.34</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>4.34</v>
       </c>
       <c r="J20" t="n">
         <v>1.1</v>
@@ -5289,16 +6004,16 @@
         <v>1.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.1</v>
+        <v>1.72</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1</v>
+        <v>1.72</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>3.37</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -5334,7 +6049,7 @@
         <v>1</v>
       </c>
       <c r="AD20" t="n">
-        <v>1</v>
+        <v>3.37</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -5347,7 +6062,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1</v>
+        <v>4.34</v>
       </c>
       <c r="C21" t="n">
         <v>1.1</v>
@@ -5356,7 +6071,7 @@
         <v>1.1</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1</v>
+        <v>4.34</v>
       </c>
       <c r="F21" t="n">
         <v>1.1</v>
@@ -5365,10 +6080,10 @@
         <v>1.1</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1</v>
+        <v>4.34</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>4.34</v>
       </c>
       <c r="J21" t="n">
         <v>1.1</v>
@@ -5386,16 +6101,16 @@
         <v>1.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.1</v>
+        <v>1.72</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1</v>
+        <v>1.72</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>3.37</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -5431,7 +6146,7 @@
         <v>1</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>3.37</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -5444,94 +6159,94 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25.24</v>
+        <v>22.12</v>
       </c>
       <c r="C22" t="n">
-        <v>25.24</v>
+        <v>12.93</v>
       </c>
       <c r="D22" t="n">
-        <v>25.24</v>
+        <v>19.84</v>
       </c>
       <c r="E22" t="n">
-        <v>25.24</v>
+        <v>15.11</v>
       </c>
       <c r="F22" t="n">
-        <v>25.24</v>
+        <v>13.46</v>
       </c>
       <c r="G22" t="n">
-        <v>25.24</v>
+        <v>13.52</v>
       </c>
       <c r="H22" t="n">
-        <v>25.24</v>
+        <v>22.79</v>
       </c>
       <c r="I22" t="n">
-        <v>25.24</v>
+        <v>22.81</v>
       </c>
       <c r="J22" t="n">
-        <v>25.24</v>
+        <v>20.43</v>
       </c>
       <c r="K22" t="n">
-        <v>25.24</v>
+        <v>20.52</v>
       </c>
       <c r="L22" t="n">
-        <v>25.24</v>
+        <v>20.55</v>
       </c>
       <c r="M22" t="n">
-        <v>25.24</v>
+        <v>21.11</v>
       </c>
       <c r="N22" t="n">
-        <v>25.24</v>
+        <v>21.14</v>
       </c>
       <c r="O22" t="n">
-        <v>25.24</v>
+        <v>21.92</v>
       </c>
       <c r="P22" t="n">
-        <v>25.24</v>
+        <v>22.16</v>
       </c>
       <c r="Q22" t="n">
-        <v>93.58</v>
+        <v>24.05</v>
       </c>
       <c r="R22" t="n">
-        <v>93.58</v>
+        <v>26.66</v>
       </c>
       <c r="S22" t="n">
-        <v>93.58</v>
+        <v>26.83</v>
       </c>
       <c r="T22" t="n">
-        <v>93.58</v>
+        <v>29.05</v>
       </c>
       <c r="U22" t="n">
-        <v>93.58</v>
+        <v>29.7</v>
       </c>
       <c r="V22" t="n">
-        <v>93.58</v>
+        <v>36.87</v>
       </c>
       <c r="W22" t="n">
-        <v>93.58</v>
+        <v>38.99</v>
       </c>
       <c r="X22" t="n">
-        <v>93.58</v>
+        <v>39.37</v>
       </c>
       <c r="Y22" t="n">
-        <v>93.58</v>
+        <v>39.99</v>
       </c>
       <c r="Z22" t="n">
-        <v>93.58</v>
+        <v>41.12</v>
       </c>
       <c r="AA22" t="n">
-        <v>93.58</v>
+        <v>43.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>93.58</v>
+        <v>44.68</v>
       </c>
       <c r="AC22" t="n">
-        <v>93.58</v>
+        <v>46.02</v>
       </c>
       <c r="AD22" t="n">
-        <v>93.58</v>
+        <v>48.43</v>
       </c>
       <c r="AE22" t="n">
-        <v>93.58</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="23">
@@ -5541,94 +6256,94 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>337691</v>
+        <v>226405</v>
       </c>
       <c r="C23" t="n">
-        <v>337691</v>
+        <v>223887</v>
       </c>
       <c r="D23" t="n">
-        <v>337691</v>
+        <v>223887</v>
       </c>
       <c r="E23" t="n">
-        <v>337691</v>
+        <v>227450</v>
       </c>
       <c r="F23" t="n">
-        <v>337691</v>
+        <v>224479</v>
       </c>
       <c r="G23" t="n">
-        <v>337691</v>
+        <v>224552</v>
       </c>
       <c r="H23" t="n">
-        <v>337691</v>
+        <v>227157</v>
       </c>
       <c r="I23" t="n">
-        <v>337691</v>
+        <v>227182</v>
       </c>
       <c r="J23" t="n">
-        <v>337691</v>
+        <v>224553</v>
       </c>
       <c r="K23" t="n">
-        <v>337691</v>
+        <v>224659</v>
       </c>
       <c r="L23" t="n">
-        <v>337691</v>
+        <v>224686</v>
       </c>
       <c r="M23" t="n">
-        <v>337691</v>
+        <v>225324</v>
       </c>
       <c r="N23" t="n">
-        <v>337691</v>
+        <v>225351</v>
       </c>
       <c r="O23" t="n">
-        <v>337691</v>
+        <v>229126</v>
       </c>
       <c r="P23" t="n">
-        <v>337691</v>
+        <v>229396</v>
       </c>
       <c r="Q23" t="n">
-        <v>655750</v>
+        <v>560387</v>
       </c>
       <c r="R23" t="n">
-        <v>655750</v>
+        <v>560663</v>
       </c>
       <c r="S23" t="n">
-        <v>655750</v>
+        <v>563509</v>
       </c>
       <c r="T23" t="n">
-        <v>655750</v>
+        <v>569413</v>
       </c>
       <c r="U23" t="n">
-        <v>655750</v>
+        <v>568829</v>
       </c>
       <c r="V23" t="n">
-        <v>655750</v>
+        <v>623210</v>
       </c>
       <c r="W23" t="n">
-        <v>655750</v>
+        <v>625783</v>
       </c>
       <c r="X23" t="n">
-        <v>655750</v>
+        <v>581208</v>
       </c>
       <c r="Y23" t="n">
-        <v>655750</v>
+        <v>625405</v>
       </c>
       <c r="Z23" t="n">
-        <v>655750</v>
+        <v>626593</v>
       </c>
       <c r="AA23" t="n">
-        <v>655750</v>
+        <v>626979</v>
       </c>
       <c r="AB23" t="n">
-        <v>655750</v>
+        <v>628398</v>
       </c>
       <c r="AC23" t="n">
-        <v>655750</v>
+        <v>630101</v>
       </c>
       <c r="AD23" t="n">
-        <v>655750</v>
+        <v>630151</v>
       </c>
       <c r="AE23" t="n">
-        <v>655750</v>
+        <v>589789</v>
       </c>
     </row>
     <row r="24">
@@ -5893,152 +6608,152 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kasembon Park</t>
+          <t>SAWAH GENTING</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kasembon Park</t>
+          <t>Desa Wisata Pujonkidul</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Kasembon Park</t>
+          <t>SAWAH GENTING</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kasembon Park</t>
+          <t>Air Terjun Coban Talun</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kasembon Park</t>
+          <t>Desa Wisata Pujonkidul</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Kasembon Park</t>
+          <t>Desa Wisata Pujonkidul</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kasembon Park</t>
+          <t>SAWAH GENTING</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Kasembon Park</t>
+          <t>SAWAH GENTING</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Kasembon Park</t>
+          <t>SAWAH GENTING</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Kasembon Park</t>
+          <t>SAWAH GENTING</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Kasembon Park</t>
+          <t>SAWAH GENTING</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Kasembon Park</t>
+          <t>SAWAH GENTING</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Kasembon Park</t>
+          <t>SAWAH GENTING</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Kasembon Park</t>
+          <t>SAWAH GENTING</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kasembon Park</t>
+          <t>SAWAH GENTING</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>The Legend Star - Jawa Timur Park 3</t>
+          <t>Taman Indragiri Malang</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>The Legend Star - Jawa Timur Park 3</t>
+          <t>Taman Indragiri Malang</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>The Legend Star - Jawa Timur Park 3</t>
+          <t>Taman Indragiri Malang</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>The Legend Star - Jawa Timur Park 3</t>
+          <t>Taman Indragiri Malang</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>The Legend Star - Jawa Timur Park 3</t>
+          <t>Taman Indragiri Malang</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>The Legend Star - Jawa Timur Park 3</t>
+          <t>Taman Indragiri Malang</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>The Legend Star - Jawa Timur Park 3</t>
+          <t>Taman Indragiri Malang</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>The Legend Star - Jawa Timur Park 3</t>
+          <t>Taman Indragiri Malang</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>The Legend Star - Jawa Timur Park 3</t>
+          <t>Taman Indragiri Malang</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>The Legend Star - Jawa Timur Park 3</t>
+          <t>Taman Indragiri Malang</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>The Legend Star - Jawa Timur Park 3</t>
+          <t>Taman Indragiri Malang</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>The Legend Star - Jawa Timur Park 3</t>
+          <t>Taman Indragiri Malang</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>The Legend Star - Jawa Timur Park 3</t>
+          <t>Taman Indragiri Malang</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>The Legend Star - Jawa Timur Park 3</t>
+          <t>Taman Indragiri Malang</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>The Legend Star - Jawa Timur Park 3</t>
+          <t>Taman Indragiri Malang</t>
         </is>
       </c>
     </row>
@@ -6049,94 +6764,94 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="C27" t="n">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="D27" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="E27" t="n">
         <v>12000</v>
       </c>
       <c r="F27" t="n">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="G27" t="n">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="H27" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="I27" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="J27" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="K27" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="L27" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="M27" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="N27" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="O27" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="P27" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="Q27" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="R27" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="S27" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="T27" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="U27" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="V27" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="W27" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="X27" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="Y27" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="Z27" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="AA27" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="AB27" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="AC27" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="AD27" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="AE27" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="28">
@@ -6147,152 +6862,152 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>Warung Jawa Sohibul Barokah</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Warung Jawa Sohibul Barokah</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Warung Jawa Sohibul Barokah</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Warung Jawa Sohibul Barokah</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Warung Biru Lesti</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Warung Biru Lesti</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Warung Biru Lesti</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Warung Biru Lesti</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Warung Biru Lesti</t>
-        </is>
-      </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Warung Biru Lesti</t>
+          <t>Warung Sumber Rejeki 2</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Warung Biru Lesti</t>
+          <t>Warung Sumber Rejeki 2</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Niki Kopitiam Malang</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
         <is>
           <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>Sego Tempong by Cak Uut</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Sego Tempong by Cak Uut</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Sego Tempong by Cak Uut</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Sego Tempong by Cak Uut</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Sego Tempong by Cak Uut</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>Sego Tempong by Cak Uut</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Sego Tempong by Cak Uut</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Sego Tempong by Cak Uut</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>Sego Tempong by Cak Uut</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>Sego Tempong by Cak Uut</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Sego Tempong by Cak Uut</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>Sego Tempong by Cak Uut</t>
-        </is>
-      </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>Sego Tempong by Cak Uut</t>
+          <t>Niki Kopitiam Malang</t>
         </is>
       </c>
     </row>
@@ -6348,49 +7063,49 @@
         <v>15000</v>
       </c>
       <c r="Q29" t="n">
-        <v>39000</v>
+        <v>40250</v>
       </c>
       <c r="R29" t="n">
         <v>39000</v>
       </c>
       <c r="S29" t="n">
-        <v>39000</v>
+        <v>40250</v>
       </c>
       <c r="T29" t="n">
-        <v>39000</v>
+        <v>40250</v>
       </c>
       <c r="U29" t="n">
-        <v>39000</v>
+        <v>40250</v>
       </c>
       <c r="V29" t="n">
-        <v>39000</v>
+        <v>40250</v>
       </c>
       <c r="W29" t="n">
-        <v>39000</v>
+        <v>40250</v>
       </c>
       <c r="X29" t="n">
-        <v>39000</v>
+        <v>40250</v>
       </c>
       <c r="Y29" t="n">
-        <v>39000</v>
+        <v>40250</v>
       </c>
       <c r="Z29" t="n">
-        <v>39000</v>
+        <v>40250</v>
       </c>
       <c r="AA29" t="n">
-        <v>39000</v>
+        <v>40250</v>
       </c>
       <c r="AB29" t="n">
-        <v>39000</v>
+        <v>40250</v>
       </c>
       <c r="AC29" t="n">
-        <v>39000</v>
+        <v>40250</v>
       </c>
       <c r="AD29" t="n">
         <v>39000</v>
       </c>
       <c r="AE29" t="n">
-        <v>39000</v>
+        <v>40250</v>
       </c>
     </row>
     <row r="30">
@@ -6401,152 +7116,152 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Waroeng Gaul Oeloeng</t>
+          <t>Warung Sumber Rejeki 2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Waroeng Gaul Oeloeng</t>
+          <t>Waroeng Watu Gong</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Waroeng Gaul Oeloeng</t>
+          <t>Warung Jawa Sohibul Barokah</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Waroeng Gaul Oeloeng</t>
+          <t>Warung Berkah</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Waroeng Gaul Oeloeng</t>
+          <t>Waroeng Watu Gong</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Waroeng Gaul Oeloeng</t>
+          <t>Waroeng Watu Gong</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Waroeng Gaul Oeloeng</t>
+          <t>Warung Sumber Rejeki 2</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Waroeng Gaul Oeloeng</t>
+          <t>Warung Sumber Rejeki 2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Waroeng Gaul Oeloeng</t>
+          <t>Warung Jawa Sohibul Barokah</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Waroeng Gaul Oeloeng</t>
+          <t>Warung Jawa Sohibul Barokah</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Waroeng Gaul Oeloeng</t>
+          <t>Warung Jawa Sohibul Barokah</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Waroeng Gaul Oeloeng</t>
+          <t>Warung Jawa Sohibul Barokah</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Waroeng Gaul Oeloeng</t>
+          <t>Warung Jawa Sohibul Barokah</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Waroeng Gaul Oeloeng</t>
+          <t>Warung Jawa Sohibul Barokah</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Waroeng Gaul Oeloeng</t>
+          <t>Warung Jawa Sohibul Barokah</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Iga Bakar Saudara</t>
+          <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Iga Bakar Saudara</t>
+          <t>Niki Kopitiam Malang</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Iga Bakar Saudara</t>
+          <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>Iga Bakar Saudara</t>
+          <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>Iga Bakar Saudara</t>
+          <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Iga Bakar Saudara</t>
+          <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Iga Bakar Saudara</t>
+          <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Iga Bakar Saudara</t>
+          <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>Iga Bakar Saudara</t>
+          <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>Iga Bakar Saudara</t>
+          <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Iga Bakar Saudara</t>
+          <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Iga Bakar Saudara</t>
+          <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Iga Bakar Saudara</t>
+          <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>Iga Bakar Saudara</t>
+          <t>Niki Kopitiam Malang</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>Iga Bakar Saudara</t>
+          <t>Sego Tempong by Cak Uut</t>
         </is>
       </c>
     </row>
@@ -6557,94 +7272,94 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>15400</v>
+        <v>15000</v>
       </c>
       <c r="C31" t="n">
-        <v>15400</v>
+        <v>15250</v>
       </c>
       <c r="D31" t="n">
-        <v>15400</v>
+        <v>15000</v>
       </c>
       <c r="E31" t="n">
-        <v>15400</v>
+        <v>15000</v>
       </c>
       <c r="F31" t="n">
-        <v>15400</v>
+        <v>15250</v>
       </c>
       <c r="G31" t="n">
-        <v>15400</v>
+        <v>15250</v>
       </c>
       <c r="H31" t="n">
-        <v>15400</v>
+        <v>15000</v>
       </c>
       <c r="I31" t="n">
-        <v>15400</v>
+        <v>15000</v>
       </c>
       <c r="J31" t="n">
-        <v>15400</v>
+        <v>15000</v>
       </c>
       <c r="K31" t="n">
-        <v>15400</v>
+        <v>15000</v>
       </c>
       <c r="L31" t="n">
-        <v>15400</v>
+        <v>15000</v>
       </c>
       <c r="M31" t="n">
-        <v>15400</v>
+        <v>15000</v>
       </c>
       <c r="N31" t="n">
-        <v>15400</v>
+        <v>15000</v>
       </c>
       <c r="O31" t="n">
-        <v>15400</v>
+        <v>15000</v>
       </c>
       <c r="P31" t="n">
-        <v>15400</v>
+        <v>15000</v>
       </c>
       <c r="Q31" t="n">
-        <v>40000</v>
+        <v>39000</v>
       </c>
       <c r="R31" t="n">
-        <v>40000</v>
+        <v>40250</v>
       </c>
       <c r="S31" t="n">
-        <v>40000</v>
+        <v>39000</v>
       </c>
       <c r="T31" t="n">
-        <v>40000</v>
+        <v>39000</v>
       </c>
       <c r="U31" t="n">
-        <v>40000</v>
+        <v>39000</v>
       </c>
       <c r="V31" t="n">
-        <v>40000</v>
+        <v>39000</v>
       </c>
       <c r="W31" t="n">
-        <v>40000</v>
+        <v>39000</v>
       </c>
       <c r="X31" t="n">
-        <v>40000</v>
+        <v>39000</v>
       </c>
       <c r="Y31" t="n">
-        <v>40000</v>
+        <v>39000</v>
       </c>
       <c r="Z31" t="n">
-        <v>40000</v>
+        <v>39000</v>
       </c>
       <c r="AA31" t="n">
-        <v>40000</v>
+        <v>39000</v>
       </c>
       <c r="AB31" t="n">
-        <v>40000</v>
+        <v>39000</v>
       </c>
       <c r="AC31" t="n">
-        <v>40000</v>
+        <v>39000</v>
       </c>
       <c r="AD31" t="n">
-        <v>40000</v>
+        <v>40250</v>
       </c>
       <c r="AE31" t="n">
-        <v>40000</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="32">
@@ -7005,94 +7720,94 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="C35" t="n">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="D35" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="E35" t="n">
         <v>12000</v>
       </c>
       <c r="F35" t="n">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="G35" t="n">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="H35" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="I35" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="J35" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="K35" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="L35" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="M35" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="N35" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="O35" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="P35" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="Q35" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="R35" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="S35" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="T35" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="U35" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="V35" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="W35" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="X35" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="Y35" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="Z35" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="AA35" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="AB35" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="AC35" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="AD35" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
       <c r="AE35" t="n">
-        <v>89100</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="36">
@@ -7102,94 +7817,94 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>30400</v>
+        <v>30000</v>
       </c>
       <c r="C36" t="n">
-        <v>30400</v>
+        <v>30250</v>
       </c>
       <c r="D36" t="n">
-        <v>30400</v>
+        <v>30000</v>
       </c>
       <c r="E36" t="n">
-        <v>30400</v>
+        <v>30000</v>
       </c>
       <c r="F36" t="n">
-        <v>30400</v>
+        <v>30250</v>
       </c>
       <c r="G36" t="n">
-        <v>30400</v>
+        <v>30250</v>
       </c>
       <c r="H36" t="n">
-        <v>30400</v>
+        <v>30000</v>
       </c>
       <c r="I36" t="n">
-        <v>30400</v>
+        <v>30000</v>
       </c>
       <c r="J36" t="n">
-        <v>30400</v>
+        <v>30000</v>
       </c>
       <c r="K36" t="n">
-        <v>30400</v>
+        <v>30000</v>
       </c>
       <c r="L36" t="n">
-        <v>30400</v>
+        <v>30000</v>
       </c>
       <c r="M36" t="n">
-        <v>30400</v>
+        <v>30000</v>
       </c>
       <c r="N36" t="n">
-        <v>30400</v>
+        <v>30000</v>
       </c>
       <c r="O36" t="n">
-        <v>30400</v>
+        <v>30000</v>
       </c>
       <c r="P36" t="n">
-        <v>30400</v>
+        <v>30000</v>
       </c>
       <c r="Q36" t="n">
-        <v>79000</v>
+        <v>79250</v>
       </c>
       <c r="R36" t="n">
-        <v>79000</v>
+        <v>79250</v>
       </c>
       <c r="S36" t="n">
-        <v>79000</v>
+        <v>79250</v>
       </c>
       <c r="T36" t="n">
-        <v>79000</v>
+        <v>79250</v>
       </c>
       <c r="U36" t="n">
-        <v>79000</v>
+        <v>79250</v>
       </c>
       <c r="V36" t="n">
-        <v>79000</v>
+        <v>79250</v>
       </c>
       <c r="W36" t="n">
-        <v>79000</v>
+        <v>79250</v>
       </c>
       <c r="X36" t="n">
-        <v>79000</v>
+        <v>79250</v>
       </c>
       <c r="Y36" t="n">
-        <v>79000</v>
+        <v>79250</v>
       </c>
       <c r="Z36" t="n">
-        <v>79000</v>
+        <v>79250</v>
       </c>
       <c r="AA36" t="n">
-        <v>79000</v>
+        <v>79250</v>
       </c>
       <c r="AB36" t="n">
-        <v>79000</v>
+        <v>79250</v>
       </c>
       <c r="AC36" t="n">
-        <v>79000</v>
+        <v>79250</v>
       </c>
       <c r="AD36" t="n">
-        <v>79000</v>
+        <v>79250</v>
       </c>
       <c r="AE36" t="n">
-        <v>79000</v>
+        <v>79250</v>
       </c>
     </row>
     <row r="37">
@@ -7199,94 +7914,94 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>145570</v>
+        <v>31579</v>
       </c>
       <c r="C37" t="n">
-        <v>145570</v>
+        <v>31616</v>
       </c>
       <c r="D37" t="n">
-        <v>145570</v>
+        <v>32117</v>
       </c>
       <c r="E37" t="n">
-        <v>145570</v>
+        <v>32124</v>
       </c>
       <c r="F37" t="n">
-        <v>145570</v>
+        <v>32209</v>
       </c>
       <c r="G37" t="n">
-        <v>145570</v>
+        <v>32281</v>
       </c>
       <c r="H37" t="n">
-        <v>145570</v>
+        <v>32331</v>
       </c>
       <c r="I37" t="n">
-        <v>145570</v>
+        <v>32356</v>
       </c>
       <c r="J37" t="n">
-        <v>145570</v>
+        <v>32781</v>
       </c>
       <c r="K37" t="n">
-        <v>145570</v>
+        <v>32888</v>
       </c>
       <c r="L37" t="n">
-        <v>145570</v>
+        <v>32915</v>
       </c>
       <c r="M37" t="n">
-        <v>145570</v>
+        <v>33553</v>
       </c>
       <c r="N37" t="n">
-        <v>145570</v>
+        <v>33581</v>
       </c>
       <c r="O37" t="n">
-        <v>145570</v>
+        <v>34300</v>
       </c>
       <c r="P37" t="n">
-        <v>145570</v>
+        <v>34571</v>
       </c>
       <c r="Q37" t="n">
-        <v>129311</v>
+        <v>39949</v>
       </c>
       <c r="R37" t="n">
-        <v>129311</v>
+        <v>40223</v>
       </c>
       <c r="S37" t="n">
-        <v>129311</v>
+        <v>43071</v>
       </c>
       <c r="T37" t="n">
-        <v>129311</v>
+        <v>45575</v>
       </c>
       <c r="U37" t="n">
-        <v>129311</v>
+        <v>46306</v>
       </c>
       <c r="V37" t="n">
-        <v>129311</v>
+        <v>54371</v>
       </c>
       <c r="W37" t="n">
-        <v>129311</v>
+        <v>56758</v>
       </c>
       <c r="X37" t="n">
-        <v>129311</v>
+        <v>57183</v>
       </c>
       <c r="Y37" t="n">
-        <v>129311</v>
+        <v>57883</v>
       </c>
       <c r="Z37" t="n">
-        <v>129311</v>
+        <v>59155</v>
       </c>
       <c r="AA37" t="n">
-        <v>129311</v>
+        <v>61540</v>
       </c>
       <c r="AB37" t="n">
-        <v>129311</v>
+        <v>63159</v>
       </c>
       <c r="AC37" t="n">
-        <v>129311</v>
+        <v>64662</v>
       </c>
       <c r="AD37" t="n">
-        <v>129311</v>
+        <v>64713</v>
       </c>
       <c r="AE37" t="n">
-        <v>129311</v>
+        <v>67351</v>
       </c>
     </row>
     <row r="38">
@@ -7296,7 +8011,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.1</v>
+        <v>1.72</v>
       </c>
       <c r="C38" t="n">
         <v>1.1</v>
@@ -7305,7 +8020,7 @@
         <v>1.1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.1</v>
+        <v>1.72</v>
       </c>
       <c r="F38" t="n">
         <v>1.1</v>
@@ -7314,10 +8029,10 @@
         <v>1.1</v>
       </c>
       <c r="H38" t="n">
-        <v>1.1</v>
+        <v>1.72</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>1.72</v>
       </c>
       <c r="J38" t="n">
         <v>1.1</v>
@@ -7335,55 +8050,55 @@
         <v>1.1</v>
       </c>
       <c r="O38" t="n">
-        <v>1.1</v>
+        <v>4.34</v>
       </c>
       <c r="P38" t="n">
-        <v>1.1</v>
+        <v>4.34</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>3.37</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>3.37</v>
       </c>
       <c r="T38" t="n">
-        <v>1</v>
+        <v>3.37</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>3.37</v>
       </c>
       <c r="V38" t="n">
-        <v>1</v>
+        <v>3.37</v>
       </c>
       <c r="W38" t="n">
-        <v>1</v>
+        <v>3.37</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>3.37</v>
       </c>
       <c r="Y38" t="n">
-        <v>1</v>
+        <v>3.37</v>
       </c>
       <c r="Z38" t="n">
-        <v>1</v>
+        <v>3.37</v>
       </c>
       <c r="AA38" t="n">
-        <v>1</v>
+        <v>3.37</v>
       </c>
       <c r="AB38" t="n">
-        <v>1</v>
+        <v>3.37</v>
       </c>
       <c r="AC38" t="n">
-        <v>1</v>
+        <v>3.37</v>
       </c>
       <c r="AD38" t="n">
         <v>1</v>
       </c>
       <c r="AE38" t="n">
-        <v>1</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="39">
@@ -7393,94 +8108,94 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>36.29</v>
+        <v>0.85</v>
       </c>
       <c r="C39" t="n">
-        <v>36.29</v>
+        <v>10.56</v>
       </c>
       <c r="D39" t="n">
-        <v>36.29</v>
+        <v>6.76</v>
       </c>
       <c r="E39" t="n">
-        <v>36.29</v>
+        <v>4.65</v>
       </c>
       <c r="F39" t="n">
-        <v>36.29</v>
+        <v>10.56</v>
       </c>
       <c r="G39" t="n">
-        <v>36.29</v>
+        <v>10.56</v>
       </c>
       <c r="H39" t="n">
-        <v>36.29</v>
+        <v>0.85</v>
       </c>
       <c r="I39" t="n">
-        <v>36.29</v>
+        <v>0.85</v>
       </c>
       <c r="J39" t="n">
-        <v>36.29</v>
+        <v>6.76</v>
       </c>
       <c r="K39" t="n">
-        <v>36.29</v>
+        <v>6.76</v>
       </c>
       <c r="L39" t="n">
-        <v>36.29</v>
+        <v>6.76</v>
       </c>
       <c r="M39" t="n">
-        <v>36.29</v>
+        <v>6.76</v>
       </c>
       <c r="N39" t="n">
-        <v>36.29</v>
+        <v>6.76</v>
       </c>
       <c r="O39" t="n">
-        <v>36.29</v>
+        <v>3.37</v>
       </c>
       <c r="P39" t="n">
-        <v>36.29</v>
+        <v>3.37</v>
       </c>
       <c r="Q39" t="n">
-        <v>18.05</v>
+        <v>4.28</v>
       </c>
       <c r="R39" t="n">
-        <v>18.05</v>
+        <v>3.81</v>
       </c>
       <c r="S39" t="n">
-        <v>18.05</v>
+        <v>4.28</v>
       </c>
       <c r="T39" t="n">
-        <v>18.05</v>
+        <v>4.28</v>
       </c>
       <c r="U39" t="n">
-        <v>18.05</v>
+        <v>4.28</v>
       </c>
       <c r="V39" t="n">
-        <v>18.05</v>
+        <v>4.28</v>
       </c>
       <c r="W39" t="n">
-        <v>18.05</v>
+        <v>4.28</v>
       </c>
       <c r="X39" t="n">
-        <v>18.05</v>
+        <v>4.28</v>
       </c>
       <c r="Y39" t="n">
-        <v>18.05</v>
+        <v>4.28</v>
       </c>
       <c r="Z39" t="n">
-        <v>18.05</v>
+        <v>4.28</v>
       </c>
       <c r="AA39" t="n">
-        <v>18.05</v>
+        <v>4.28</v>
       </c>
       <c r="AB39" t="n">
-        <v>18.05</v>
+        <v>4.28</v>
       </c>
       <c r="AC39" t="n">
-        <v>18.05</v>
+        <v>4.28</v>
       </c>
       <c r="AD39" t="n">
-        <v>18.05</v>
+        <v>3.81</v>
       </c>
       <c r="AE39" t="n">
-        <v>18.05</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="40">
@@ -7490,94 +8205,94 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>66.77</v>
+        <v>3.37</v>
       </c>
       <c r="C40" t="n">
-        <v>66.77</v>
+        <v>3.51</v>
       </c>
       <c r="D40" t="n">
-        <v>66.77</v>
+        <v>0.85</v>
       </c>
       <c r="E40" t="n">
-        <v>66.77</v>
+        <v>7.07</v>
       </c>
       <c r="F40" t="n">
-        <v>66.77</v>
+        <v>3.51</v>
       </c>
       <c r="G40" t="n">
-        <v>66.77</v>
+        <v>3.51</v>
       </c>
       <c r="H40" t="n">
-        <v>66.77</v>
+        <v>3.37</v>
       </c>
       <c r="I40" t="n">
-        <v>66.77</v>
+        <v>3.37</v>
       </c>
       <c r="J40" t="n">
-        <v>66.77</v>
+        <v>0.85</v>
       </c>
       <c r="K40" t="n">
-        <v>66.77</v>
+        <v>0.85</v>
       </c>
       <c r="L40" t="n">
-        <v>66.77</v>
+        <v>0.85</v>
       </c>
       <c r="M40" t="n">
-        <v>66.77</v>
+        <v>0.85</v>
       </c>
       <c r="N40" t="n">
-        <v>66.77</v>
+        <v>0.85</v>
       </c>
       <c r="O40" t="n">
-        <v>66.77</v>
+        <v>0.85</v>
       </c>
       <c r="P40" t="n">
-        <v>66.77</v>
+        <v>0.85</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.31</v>
+        <v>3.81</v>
       </c>
       <c r="R40" t="n">
-        <v>2.31</v>
+        <v>4.28</v>
       </c>
       <c r="S40" t="n">
-        <v>2.31</v>
+        <v>3.81</v>
       </c>
       <c r="T40" t="n">
-        <v>2.31</v>
+        <v>3.81</v>
       </c>
       <c r="U40" t="n">
-        <v>2.31</v>
+        <v>3.81</v>
       </c>
       <c r="V40" t="n">
-        <v>2.31</v>
+        <v>3.81</v>
       </c>
       <c r="W40" t="n">
-        <v>2.31</v>
+        <v>3.81</v>
       </c>
       <c r="X40" t="n">
-        <v>2.31</v>
+        <v>3.81</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.31</v>
+        <v>3.81</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.31</v>
+        <v>3.81</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.31</v>
+        <v>3.81</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.31</v>
+        <v>3.81</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.31</v>
+        <v>3.81</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.31</v>
+        <v>4.28</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.31</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="41">
@@ -7587,94 +8302,94 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>104.16</v>
+        <v>5.95</v>
       </c>
       <c r="C41" t="n">
-        <v>104.16</v>
+        <v>15.17</v>
       </c>
       <c r="D41" t="n">
-        <v>104.16</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>104.16</v>
+        <v>13.44</v>
       </c>
       <c r="F41" t="n">
-        <v>104.16</v>
+        <v>15.17</v>
       </c>
       <c r="G41" t="n">
-        <v>104.16</v>
+        <v>15.17</v>
       </c>
       <c r="H41" t="n">
-        <v>104.16</v>
+        <v>5.95</v>
       </c>
       <c r="I41" t="n">
-        <v>104.16</v>
+        <v>5.95</v>
       </c>
       <c r="J41" t="n">
-        <v>104.16</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>104.16</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>104.16</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>104.16</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>104.16</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>104.16</v>
+        <v>8.57</v>
       </c>
       <c r="P41" t="n">
-        <v>104.16</v>
+        <v>8.57</v>
       </c>
       <c r="Q41" t="n">
-        <v>21.36</v>
+        <v>11.46</v>
       </c>
       <c r="R41" t="n">
-        <v>21.36</v>
+        <v>9.09</v>
       </c>
       <c r="S41" t="n">
-        <v>21.36</v>
+        <v>11.46</v>
       </c>
       <c r="T41" t="n">
-        <v>21.36</v>
+        <v>11.46</v>
       </c>
       <c r="U41" t="n">
-        <v>21.36</v>
+        <v>11.46</v>
       </c>
       <c r="V41" t="n">
-        <v>21.36</v>
+        <v>11.46</v>
       </c>
       <c r="W41" t="n">
-        <v>21.36</v>
+        <v>11.46</v>
       </c>
       <c r="X41" t="n">
-        <v>21.36</v>
+        <v>11.46</v>
       </c>
       <c r="Y41" t="n">
-        <v>21.36</v>
+        <v>11.46</v>
       </c>
       <c r="Z41" t="n">
-        <v>21.36</v>
+        <v>11.46</v>
       </c>
       <c r="AA41" t="n">
-        <v>21.36</v>
+        <v>11.46</v>
       </c>
       <c r="AB41" t="n">
-        <v>21.36</v>
+        <v>11.46</v>
       </c>
       <c r="AC41" t="n">
-        <v>21.36</v>
+        <v>11.46</v>
       </c>
       <c r="AD41" t="n">
-        <v>21.36</v>
+        <v>9.09</v>
       </c>
       <c r="AE41" t="n">
-        <v>21.36</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="42">
@@ -7684,94 +8399,94 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>187970</v>
+        <v>74079</v>
       </c>
       <c r="C42" t="n">
-        <v>187970</v>
+        <v>74866</v>
       </c>
       <c r="D42" t="n">
-        <v>187970</v>
+        <v>74617</v>
       </c>
       <c r="E42" t="n">
-        <v>187970</v>
+        <v>74124</v>
       </c>
       <c r="F42" t="n">
-        <v>187970</v>
+        <v>75459</v>
       </c>
       <c r="G42" t="n">
-        <v>187970</v>
+        <v>75531</v>
       </c>
       <c r="H42" t="n">
-        <v>187970</v>
+        <v>74831</v>
       </c>
       <c r="I42" t="n">
-        <v>187970</v>
+        <v>74856</v>
       </c>
       <c r="J42" t="n">
-        <v>187970</v>
+        <v>75281</v>
       </c>
       <c r="K42" t="n">
-        <v>187970</v>
+        <v>75388</v>
       </c>
       <c r="L42" t="n">
-        <v>187970</v>
+        <v>75415</v>
       </c>
       <c r="M42" t="n">
-        <v>187970</v>
+        <v>76053</v>
       </c>
       <c r="N42" t="n">
-        <v>187970</v>
+        <v>76081</v>
       </c>
       <c r="O42" t="n">
-        <v>187970</v>
+        <v>76800</v>
       </c>
       <c r="P42" t="n">
-        <v>187970</v>
+        <v>77071</v>
       </c>
       <c r="Q42" t="n">
-        <v>297411</v>
+        <v>199199</v>
       </c>
       <c r="R42" t="n">
-        <v>297411</v>
+        <v>199473</v>
       </c>
       <c r="S42" t="n">
-        <v>297411</v>
+        <v>202321</v>
       </c>
       <c r="T42" t="n">
-        <v>297411</v>
+        <v>204825</v>
       </c>
       <c r="U42" t="n">
-        <v>297411</v>
+        <v>205556</v>
       </c>
       <c r="V42" t="n">
-        <v>297411</v>
+        <v>213621</v>
       </c>
       <c r="W42" t="n">
-        <v>297411</v>
+        <v>216008</v>
       </c>
       <c r="X42" t="n">
-        <v>297411</v>
+        <v>216433</v>
       </c>
       <c r="Y42" t="n">
-        <v>297411</v>
+        <v>217133</v>
       </c>
       <c r="Z42" t="n">
-        <v>297411</v>
+        <v>218405</v>
       </c>
       <c r="AA42" t="n">
-        <v>297411</v>
+        <v>220790</v>
       </c>
       <c r="AB42" t="n">
-        <v>297411</v>
+        <v>222409</v>
       </c>
       <c r="AC42" t="n">
-        <v>297411</v>
+        <v>223912</v>
       </c>
       <c r="AD42" t="n">
-        <v>297411</v>
+        <v>223963</v>
       </c>
       <c r="AE42" t="n">
-        <v>297411</v>
+        <v>226601</v>
       </c>
     </row>
     <row r="43">
@@ -7781,7 +8496,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="C43" t="n">
         <v>134771</v>
@@ -7790,7 +8505,7 @@
         <v>134771</v>
       </c>
       <c r="E43" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="F43" t="n">
         <v>134771</v>
@@ -7799,10 +8514,10 @@
         <v>134771</v>
       </c>
       <c r="H43" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="I43" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="J43" t="n">
         <v>134771</v>
@@ -7820,10 +8535,10 @@
         <v>134771</v>
       </c>
       <c r="O43" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="P43" t="n">
-        <v>134771</v>
+        <v>137826</v>
       </c>
       <c r="Q43" t="n">
         <v>318189</v>
@@ -7878,94 +8593,94 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>24000</v>
+        <v>24500</v>
       </c>
       <c r="C44" t="n">
-        <v>24000</v>
+        <v>25500</v>
       </c>
       <c r="D44" t="n">
-        <v>24000</v>
+        <v>24500</v>
       </c>
       <c r="E44" t="n">
-        <v>24000</v>
+        <v>24500</v>
       </c>
       <c r="F44" t="n">
-        <v>24000</v>
+        <v>25500</v>
       </c>
       <c r="G44" t="n">
-        <v>24000</v>
+        <v>25500</v>
       </c>
       <c r="H44" t="n">
-        <v>24000</v>
+        <v>24500</v>
       </c>
       <c r="I44" t="n">
-        <v>24000</v>
+        <v>24500</v>
       </c>
       <c r="J44" t="n">
-        <v>24000</v>
+        <v>24500</v>
       </c>
       <c r="K44" t="n">
-        <v>24000</v>
+        <v>24500</v>
       </c>
       <c r="L44" t="n">
-        <v>24000</v>
+        <v>24500</v>
       </c>
       <c r="M44" t="n">
-        <v>24000</v>
+        <v>24500</v>
       </c>
       <c r="N44" t="n">
-        <v>24000</v>
+        <v>24500</v>
       </c>
       <c r="O44" t="n">
-        <v>24000</v>
+        <v>24500</v>
       </c>
       <c r="P44" t="n">
-        <v>24000</v>
+        <v>24500</v>
       </c>
       <c r="Q44" t="n">
-        <v>179100</v>
+        <v>165000</v>
       </c>
       <c r="R44" t="n">
-        <v>179100</v>
+        <v>165000</v>
       </c>
       <c r="S44" t="n">
-        <v>179100</v>
+        <v>165000</v>
       </c>
       <c r="T44" t="n">
-        <v>179100</v>
+        <v>165000</v>
       </c>
       <c r="U44" t="n">
-        <v>179100</v>
+        <v>165000</v>
       </c>
       <c r="V44" t="n">
-        <v>179100</v>
+        <v>210000</v>
       </c>
       <c r="W44" t="n">
-        <v>179100</v>
+        <v>210000</v>
       </c>
       <c r="X44" t="n">
-        <v>179100</v>
+        <v>165000</v>
       </c>
       <c r="Y44" t="n">
-        <v>179100</v>
+        <v>210000</v>
       </c>
       <c r="Z44" t="n">
-        <v>179100</v>
+        <v>210000</v>
       </c>
       <c r="AA44" t="n">
-        <v>179100</v>
+        <v>210000</v>
       </c>
       <c r="AB44" t="n">
-        <v>179100</v>
+        <v>210000</v>
       </c>
       <c r="AC44" t="n">
-        <v>179100</v>
+        <v>210000</v>
       </c>
       <c r="AD44" t="n">
-        <v>179100</v>
+        <v>210000</v>
       </c>
       <c r="AE44" t="n">
-        <v>179100</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="45">
@@ -7975,94 +8690,94 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>75750</v>
+        <v>75000</v>
       </c>
       <c r="C45" t="n">
-        <v>75750</v>
+        <v>75250</v>
       </c>
       <c r="D45" t="n">
-        <v>75750</v>
+        <v>75000</v>
       </c>
       <c r="E45" t="n">
-        <v>75750</v>
+        <v>75000</v>
       </c>
       <c r="F45" t="n">
-        <v>75750</v>
+        <v>75250</v>
       </c>
       <c r="G45" t="n">
-        <v>75750</v>
+        <v>75250</v>
       </c>
       <c r="H45" t="n">
-        <v>75750</v>
+        <v>75000</v>
       </c>
       <c r="I45" t="n">
-        <v>75750</v>
+        <v>75000</v>
       </c>
       <c r="J45" t="n">
-        <v>75750</v>
+        <v>75000</v>
       </c>
       <c r="K45" t="n">
-        <v>75750</v>
+        <v>75000</v>
       </c>
       <c r="L45" t="n">
-        <v>75750</v>
+        <v>75000</v>
       </c>
       <c r="M45" t="n">
-        <v>75750</v>
+        <v>75000</v>
       </c>
       <c r="N45" t="n">
-        <v>75750</v>
+        <v>75000</v>
       </c>
       <c r="O45" t="n">
-        <v>75750</v>
+        <v>75000</v>
       </c>
       <c r="P45" t="n">
-        <v>75750</v>
+        <v>75000</v>
       </c>
       <c r="Q45" t="n">
-        <v>197250</v>
+        <v>196500</v>
       </c>
       <c r="R45" t="n">
-        <v>197250</v>
+        <v>196500</v>
       </c>
       <c r="S45" t="n">
-        <v>197250</v>
+        <v>196500</v>
       </c>
       <c r="T45" t="n">
-        <v>197250</v>
+        <v>199900</v>
       </c>
       <c r="U45" t="n">
-        <v>197250</v>
+        <v>198584</v>
       </c>
       <c r="V45" t="n">
-        <v>197250</v>
+        <v>199900</v>
       </c>
       <c r="W45" t="n">
-        <v>197250</v>
+        <v>200086</v>
       </c>
       <c r="X45" t="n">
-        <v>197250</v>
+        <v>200086</v>
       </c>
       <c r="Y45" t="n">
-        <v>197250</v>
+        <v>198584</v>
       </c>
       <c r="Z45" t="n">
-        <v>197250</v>
+        <v>198500</v>
       </c>
       <c r="AA45" t="n">
-        <v>197250</v>
+        <v>196500</v>
       </c>
       <c r="AB45" t="n">
-        <v>197250</v>
+        <v>196300</v>
       </c>
       <c r="AC45" t="n">
-        <v>197250</v>
+        <v>196500</v>
       </c>
       <c r="AD45" t="n">
-        <v>197250</v>
+        <v>196500</v>
       </c>
       <c r="AE45" t="n">
-        <v>197250</v>
+        <v>198500</v>
       </c>
     </row>
     <row r="46">
@@ -8072,94 +8787,94 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>291140</v>
+        <v>63158</v>
       </c>
       <c r="C46" t="n">
-        <v>291140</v>
+        <v>63232</v>
       </c>
       <c r="D46" t="n">
-        <v>291140</v>
+        <v>64233</v>
       </c>
       <c r="E46" t="n">
-        <v>291140</v>
+        <v>64248</v>
       </c>
       <c r="F46" t="n">
-        <v>291140</v>
+        <v>64417</v>
       </c>
       <c r="G46" t="n">
-        <v>291140</v>
+        <v>64562</v>
       </c>
       <c r="H46" t="n">
-        <v>291140</v>
+        <v>64662</v>
       </c>
       <c r="I46" t="n">
-        <v>291140</v>
+        <v>64712</v>
       </c>
       <c r="J46" t="n">
-        <v>291140</v>
+        <v>65563</v>
       </c>
       <c r="K46" t="n">
-        <v>291140</v>
+        <v>65776</v>
       </c>
       <c r="L46" t="n">
-        <v>291140</v>
+        <v>65830</v>
       </c>
       <c r="M46" t="n">
-        <v>291140</v>
+        <v>67106</v>
       </c>
       <c r="N46" t="n">
-        <v>291140</v>
+        <v>67161</v>
       </c>
       <c r="O46" t="n">
-        <v>291140</v>
+        <v>68600</v>
       </c>
       <c r="P46" t="n">
-        <v>291140</v>
+        <v>69141</v>
       </c>
       <c r="Q46" t="n">
-        <v>258622</v>
+        <v>79897</v>
       </c>
       <c r="R46" t="n">
-        <v>258622</v>
+        <v>80447</v>
       </c>
       <c r="S46" t="n">
-        <v>258622</v>
+        <v>86141</v>
       </c>
       <c r="T46" t="n">
-        <v>258622</v>
+        <v>91149</v>
       </c>
       <c r="U46" t="n">
-        <v>258622</v>
+        <v>92612</v>
       </c>
       <c r="V46" t="n">
-        <v>258622</v>
+        <v>108742</v>
       </c>
       <c r="W46" t="n">
-        <v>258622</v>
+        <v>113516</v>
       </c>
       <c r="X46" t="n">
-        <v>258622</v>
+        <v>114366</v>
       </c>
       <c r="Y46" t="n">
-        <v>258622</v>
+        <v>115765</v>
       </c>
       <c r="Z46" t="n">
-        <v>258622</v>
+        <v>118309</v>
       </c>
       <c r="AA46" t="n">
-        <v>258622</v>
+        <v>123080</v>
       </c>
       <c r="AB46" t="n">
-        <v>258622</v>
+        <v>126318</v>
       </c>
       <c r="AC46" t="n">
-        <v>258622</v>
+        <v>129324</v>
       </c>
       <c r="AD46" t="n">
-        <v>258622</v>
+        <v>129425</v>
       </c>
       <c r="AE46" t="n">
-        <v>258622</v>
+        <v>134701</v>
       </c>
     </row>
     <row r="47">
@@ -8169,94 +8884,94 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>525661</v>
+        <v>300484</v>
       </c>
       <c r="C47" t="n">
-        <v>525661</v>
+        <v>298753</v>
       </c>
       <c r="D47" t="n">
-        <v>525661</v>
+        <v>298504</v>
       </c>
       <c r="E47" t="n">
-        <v>525661</v>
+        <v>301574</v>
       </c>
       <c r="F47" t="n">
-        <v>525661</v>
+        <v>299938</v>
       </c>
       <c r="G47" t="n">
-        <v>525661</v>
+        <v>300083</v>
       </c>
       <c r="H47" t="n">
-        <v>525661</v>
+        <v>301988</v>
       </c>
       <c r="I47" t="n">
-        <v>525661</v>
+        <v>302038</v>
       </c>
       <c r="J47" t="n">
-        <v>525661</v>
+        <v>299834</v>
       </c>
       <c r="K47" t="n">
-        <v>525661</v>
+        <v>300047</v>
       </c>
       <c r="L47" t="n">
-        <v>525661</v>
+        <v>300101</v>
       </c>
       <c r="M47" t="n">
-        <v>525661</v>
+        <v>301377</v>
       </c>
       <c r="N47" t="n">
-        <v>525661</v>
+        <v>301432</v>
       </c>
       <c r="O47" t="n">
-        <v>525661</v>
+        <v>305926</v>
       </c>
       <c r="P47" t="n">
-        <v>525661</v>
+        <v>306467</v>
       </c>
       <c r="Q47" t="n">
-        <v>953161</v>
+        <v>759586</v>
       </c>
       <c r="R47" t="n">
-        <v>953161</v>
+        <v>760136</v>
       </c>
       <c r="S47" t="n">
-        <v>953161</v>
+        <v>765830</v>
       </c>
       <c r="T47" t="n">
-        <v>953161</v>
+        <v>774238</v>
       </c>
       <c r="U47" t="n">
-        <v>953161</v>
+        <v>774385</v>
       </c>
       <c r="V47" t="n">
-        <v>953161</v>
+        <v>836831</v>
       </c>
       <c r="W47" t="n">
-        <v>953161</v>
+        <v>841791</v>
       </c>
       <c r="X47" t="n">
-        <v>953161</v>
+        <v>797641</v>
       </c>
       <c r="Y47" t="n">
-        <v>953161</v>
+        <v>842538</v>
       </c>
       <c r="Z47" t="n">
-        <v>953161</v>
+        <v>844998</v>
       </c>
       <c r="AA47" t="n">
-        <v>953161</v>
+        <v>847769</v>
       </c>
       <c r="AB47" t="n">
-        <v>953161</v>
+        <v>850807</v>
       </c>
       <c r="AC47" t="n">
-        <v>953161</v>
+        <v>854013</v>
       </c>
       <c r="AD47" t="n">
-        <v>953161</v>
+        <v>854114</v>
       </c>
       <c r="AE47" t="n">
-        <v>953161</v>
+        <v>816390</v>
       </c>
     </row>
     <row r="48">
@@ -8266,94 +8981,94 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>129.4</v>
+        <v>28.07</v>
       </c>
       <c r="C48" t="n">
-        <v>129.4</v>
+        <v>28.1</v>
       </c>
       <c r="D48" t="n">
-        <v>129.4</v>
+        <v>28.55</v>
       </c>
       <c r="E48" t="n">
-        <v>129.4</v>
+        <v>28.55</v>
       </c>
       <c r="F48" t="n">
-        <v>129.4</v>
+        <v>28.63</v>
       </c>
       <c r="G48" t="n">
-        <v>129.4</v>
+        <v>28.69</v>
       </c>
       <c r="H48" t="n">
-        <v>129.4</v>
+        <v>28.74</v>
       </c>
       <c r="I48" t="n">
-        <v>129.4</v>
+        <v>28.76</v>
       </c>
       <c r="J48" t="n">
-        <v>129.4</v>
+        <v>29.14</v>
       </c>
       <c r="K48" t="n">
-        <v>129.4</v>
+        <v>29.23</v>
       </c>
       <c r="L48" t="n">
-        <v>129.4</v>
+        <v>29.26</v>
       </c>
       <c r="M48" t="n">
-        <v>129.4</v>
+        <v>29.82</v>
       </c>
       <c r="N48" t="n">
-        <v>129.4</v>
+        <v>29.85</v>
       </c>
       <c r="O48" t="n">
-        <v>129.4</v>
+        <v>30.49</v>
       </c>
       <c r="P48" t="n">
-        <v>129.4</v>
+        <v>30.73</v>
       </c>
       <c r="Q48" t="n">
-        <v>114.94</v>
+        <v>35.51</v>
       </c>
       <c r="R48" t="n">
-        <v>114.94</v>
+        <v>35.75</v>
       </c>
       <c r="S48" t="n">
-        <v>114.94</v>
+        <v>38.28</v>
       </c>
       <c r="T48" t="n">
-        <v>114.94</v>
+        <v>40.51</v>
       </c>
       <c r="U48" t="n">
-        <v>114.94</v>
+        <v>41.16</v>
       </c>
       <c r="V48" t="n">
-        <v>114.94</v>
+        <v>48.33</v>
       </c>
       <c r="W48" t="n">
-        <v>114.94</v>
+        <v>50.45</v>
       </c>
       <c r="X48" t="n">
-        <v>114.94</v>
+        <v>50.83</v>
       </c>
       <c r="Y48" t="n">
-        <v>114.94</v>
+        <v>51.45</v>
       </c>
       <c r="Z48" t="n">
-        <v>114.94</v>
+        <v>52.58</v>
       </c>
       <c r="AA48" t="n">
-        <v>114.94</v>
+        <v>54.7</v>
       </c>
       <c r="AB48" t="n">
-        <v>114.94</v>
+        <v>56.14</v>
       </c>
       <c r="AC48" t="n">
-        <v>114.94</v>
+        <v>57.48</v>
       </c>
       <c r="AD48" t="n">
-        <v>114.94</v>
+        <v>57.52</v>
       </c>
       <c r="AE48" t="n">
-        <v>114.94</v>
+        <v>59.87</v>
       </c>
     </row>
   </sheetData>
